--- a/META.xlsx
+++ b/META.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738F637F-4E77-49F5-A58C-20CC5C1AC91F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EECA3BDB-91BB-4B5D-8EFC-43109FE1DE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="53750" yWindow="420" windowWidth="24340" windowHeight="15680" activeTab="1" xr2:uid="{DF105585-55F7-489F-BFB3-1F48B85ABA8A}"/>
+    <workbookView xWindow="22310" yWindow="6660" windowWidth="15770" windowHeight="13220" xr2:uid="{DF105585-55F7-489F-BFB3-1F48B85ABA8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1093,14 +1093,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>68</xdr:col>
-      <xdr:colOff>613674</xdr:colOff>
+      <xdr:col>71</xdr:col>
+      <xdr:colOff>27521</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>68</xdr:col>
-      <xdr:colOff>613674</xdr:colOff>
+      <xdr:col>71</xdr:col>
+      <xdr:colOff>27521</xdr:colOff>
       <xdr:row>131</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
@@ -1117,7 +1117,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="43671559" y="0"/>
+          <a:off x="44931790" y="0"/>
           <a:ext cx="0" cy="21140616"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1559,7 +1559,7 @@
         <v>1</v>
       </c>
       <c r="M2" s="17">
-        <v>681</v>
+        <v>605</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -1573,10 +1573,11 @@
         <v>2</v>
       </c>
       <c r="M3" s="3">
-        <v>2572</v>
+        <f>Model!BS45</f>
+        <v>2564</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>217</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -1591,7 +1592,7 @@
       </c>
       <c r="M4" s="3">
         <f>+M3*M2</f>
-        <v>1751532</v>
+        <v>1551220</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1602,10 +1603,11 @@
         <v>4</v>
       </c>
       <c r="M5" s="3">
-        <v>69522</v>
+        <f>+Model!BS59</f>
+        <v>109590</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>217</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -1616,10 +1618,11 @@
         <v>5</v>
       </c>
       <c r="M6" s="3">
-        <v>28834</v>
+        <f>Model!BS73</f>
+        <v>58748</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>217</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1628,7 +1631,7 @@
       </c>
       <c r="M7" s="3">
         <f>+M4-M5+M6</f>
-        <v>1710844</v>
+        <v>1500378</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2843,6 +2846,12 @@
       <c r="BG9" s="6"/>
       <c r="BH9" s="6"/>
       <c r="BI9" s="6"/>
+      <c r="CC9" s="3">
+        <v>75</v>
+      </c>
+      <c r="CD9" s="3">
+        <v>112</v>
+      </c>
       <c r="CE9" s="3">
         <v>154</v>
       </c>
@@ -5291,10 +5300,11 @@
         <v>51242</v>
       </c>
       <c r="BR32" s="8">
-        <f>+BN32*1.12</f>
-        <v>54191.200000000004</v>
-      </c>
-      <c r="BS32" s="8"/>
+        <v>59893</v>
+      </c>
+      <c r="BS32" s="8">
+        <v>56311</v>
+      </c>
       <c r="BT32" s="8"/>
       <c r="BU32" s="8"/>
       <c r="BV32" s="8"/>
@@ -5385,27 +5395,27 @@
       </c>
       <c r="CT32" s="7">
         <f>SUM(BO32:BR32)</f>
-        <v>195263.2</v>
+        <v>200965</v>
       </c>
       <c r="CU32" s="7">
         <f>+CT32*1.1</f>
-        <v>214789.52000000002</v>
+        <v>221061.50000000003</v>
       </c>
       <c r="CV32" s="7">
         <f>+CU32*1.08</f>
-        <v>231972.68160000004</v>
+        <v>238746.42000000004</v>
       </c>
       <c r="CW32" s="7">
         <f>+CV32*1.08</f>
-        <v>250530.49612800006</v>
+        <v>257846.13360000006</v>
       </c>
       <c r="CX32" s="7">
         <f>+CW32*1.05</f>
-        <v>263057.02093440009</v>
+        <v>270738.4402800001</v>
       </c>
       <c r="CY32" s="7">
         <f>+CX32*1.05</f>
-        <v>276209.87198112009</v>
+        <v>284275.36229400011</v>
       </c>
     </row>
     <row r="33" spans="2:159" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5567,10 +5577,11 @@
         <v>9206</v>
       </c>
       <c r="BR33" s="6">
-        <f>+BR32-BR34</f>
-        <v>9212.5040000000008</v>
-      </c>
-      <c r="BS33" s="6"/>
+        <v>10905</v>
+      </c>
+      <c r="BS33" s="6">
+        <v>10218</v>
+      </c>
       <c r="BT33" s="6"/>
       <c r="BU33" s="6"/>
       <c r="BV33" s="6"/>
@@ -5634,27 +5645,27 @@
       </c>
       <c r="CT33" s="3">
         <f t="shared" si="27"/>
-        <v>37100.008000000002</v>
+        <v>38183.349999999977</v>
       </c>
       <c r="CU33" s="3">
         <f t="shared" si="27"/>
-        <v>40810.008799999981</v>
+        <v>42001.684999999998</v>
       </c>
       <c r="CV33" s="3">
         <f t="shared" si="27"/>
-        <v>44074.809504000004</v>
+        <v>45361.819799999997</v>
       </c>
       <c r="CW33" s="3">
         <f t="shared" si="27"/>
-        <v>47600.794264319993</v>
+        <v>48990.765383999998</v>
       </c>
       <c r="CX33" s="3">
         <f t="shared" si="27"/>
-        <v>49980.833977536007</v>
+        <v>51440.303653200011</v>
       </c>
       <c r="CY33" s="3">
         <f t="shared" si="27"/>
-        <v>52479.875676412805</v>
+        <v>54012.318835860002</v>
       </c>
     </row>
     <row r="34" spans="2:159" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5858,10 +5869,13 @@
         <v>42036</v>
       </c>
       <c r="BR34" s="6">
-        <f>+BR32*0.83</f>
-        <v>44978.696000000004</v>
-      </c>
-      <c r="BS34" s="6"/>
+        <f>+BR32-BR33</f>
+        <v>48988</v>
+      </c>
+      <c r="BS34" s="6">
+        <f>+BS32*0.83</f>
+        <v>46738.13</v>
+      </c>
       <c r="BT34" s="6"/>
       <c r="BU34" s="6"/>
       <c r="BV34" s="6"/>
@@ -5940,27 +5954,27 @@
       </c>
       <c r="CT34" s="3">
         <f t="shared" si="40"/>
-        <v>158163.19200000001</v>
+        <v>162781.65000000002</v>
       </c>
       <c r="CU34" s="3">
         <f t="shared" si="40"/>
-        <v>173979.51120000004</v>
+        <v>179059.81500000003</v>
       </c>
       <c r="CV34" s="3">
         <f t="shared" si="40"/>
-        <v>187897.87209600004</v>
+        <v>193384.60020000004</v>
       </c>
       <c r="CW34" s="3">
         <f t="shared" si="40"/>
-        <v>202929.70186368006</v>
+        <v>208855.36821600006</v>
       </c>
       <c r="CX34" s="3">
         <f t="shared" si="40"/>
-        <v>213076.18695686408</v>
+        <v>219298.13662680009</v>
       </c>
       <c r="CY34" s="3">
         <f t="shared" si="40"/>
-        <v>223729.99630470728</v>
+        <v>230263.04345814011</v>
       </c>
     </row>
     <row r="35" spans="2:159" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6122,10 +6136,11 @@
         <v>15144</v>
       </c>
       <c r="BR35" s="6">
-        <f t="shared" ref="BR35:BR36" si="41">+BN35</f>
-        <v>12180</v>
-      </c>
-      <c r="BS35" s="6"/>
+        <v>17136</v>
+      </c>
+      <c r="BS35" s="6">
+        <v>17699</v>
+      </c>
       <c r="BT35" s="6"/>
       <c r="BU35" s="6"/>
       <c r="BV35" s="6"/>
@@ -6176,39 +6191,39 @@
         <v>24655</v>
       </c>
       <c r="CQ35" s="3">
-        <f t="shared" ref="CQ35:CV35" si="42">+CP35*0.9</f>
+        <f t="shared" ref="CQ35:CV35" si="41">+CP35*0.9</f>
         <v>22189.5</v>
       </c>
       <c r="CR35" s="3">
+        <f t="shared" si="41"/>
+        <v>19970.55</v>
+      </c>
+      <c r="CS35" s="3">
+        <f t="shared" si="41"/>
+        <v>17973.494999999999</v>
+      </c>
+      <c r="CT35" s="3">
+        <f t="shared" si="41"/>
+        <v>16176.145499999999</v>
+      </c>
+      <c r="CU35" s="3">
+        <f t="shared" si="41"/>
+        <v>14558.530949999998</v>
+      </c>
+      <c r="CV35" s="3">
+        <f t="shared" si="41"/>
+        <v>13102.677854999998</v>
+      </c>
+      <c r="CW35" s="3">
+        <f t="shared" ref="CW35:CY35" si="42">+CV35*0.9</f>
+        <v>11792.410069499998</v>
+      </c>
+      <c r="CX35" s="3">
         <f t="shared" si="42"/>
-        <v>19970.55</v>
-      </c>
-      <c r="CS35" s="3">
+        <v>10613.169062549998</v>
+      </c>
+      <c r="CY35" s="3">
         <f t="shared" si="42"/>
-        <v>17973.494999999999</v>
-      </c>
-      <c r="CT35" s="3">
-        <f t="shared" si="42"/>
-        <v>16176.145499999999</v>
-      </c>
-      <c r="CU35" s="3">
-        <f t="shared" si="42"/>
-        <v>14558.530949999998</v>
-      </c>
-      <c r="CV35" s="3">
-        <f t="shared" si="42"/>
-        <v>13102.677854999998</v>
-      </c>
-      <c r="CW35" s="3">
-        <f t="shared" ref="CW35:CY35" si="43">+CV35*0.9</f>
-        <v>11792.410069499998</v>
-      </c>
-      <c r="CX35" s="3">
-        <f t="shared" si="43"/>
-        <v>10613.169062549998</v>
-      </c>
-      <c r="CY35" s="3">
-        <f t="shared" si="43"/>
         <v>9551.8521562949991</v>
       </c>
     </row>
@@ -6337,7 +6352,7 @@
         <v>4574</v>
       </c>
       <c r="BG36" s="6">
-        <f t="shared" ref="BG36:BG37" si="44">+BC36*0.9</f>
+        <f t="shared" ref="BG36:BG37" si="43">+BC36*0.9</f>
         <v>2980.8</v>
       </c>
       <c r="BH36" s="6">
@@ -6371,10 +6386,11 @@
         <v>2845</v>
       </c>
       <c r="BR36" s="6">
-        <f t="shared" si="41"/>
-        <v>3240</v>
-      </c>
-      <c r="BS36" s="6"/>
+        <v>3410</v>
+      </c>
+      <c r="BS36" s="6">
+        <v>2908</v>
+      </c>
       <c r="BT36" s="6"/>
       <c r="BU36" s="6"/>
       <c r="BV36" s="6"/>
@@ -6429,35 +6445,35 @@
         <v>14043</v>
       </c>
       <c r="CR36" s="3">
-        <f t="shared" ref="CR36:CY36" si="45">+CQ36</f>
+        <f t="shared" ref="CR36:CY36" si="44">+CQ36</f>
         <v>14043</v>
       </c>
       <c r="CS36" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>14043</v>
       </c>
       <c r="CT36" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>14043</v>
       </c>
       <c r="CU36" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>14043</v>
       </c>
       <c r="CV36" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>14043</v>
       </c>
       <c r="CW36" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>14043</v>
       </c>
       <c r="CX36" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>14043</v>
       </c>
       <c r="CY36" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>14043</v>
       </c>
     </row>
@@ -6588,7 +6604,7 @@
         <v>3085</v>
       </c>
       <c r="BG37" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>2124</v>
       </c>
       <c r="BH37" s="6">
@@ -6623,10 +6639,11 @@
         <v>3512</v>
       </c>
       <c r="BR37" s="6">
-        <f>+BQ37</f>
-        <v>3512</v>
-      </c>
-      <c r="BS37" s="6"/>
+        <v>3697</v>
+      </c>
+      <c r="BS37" s="6">
+        <v>2614</v>
+      </c>
       <c r="BT37" s="6"/>
       <c r="BU37" s="6"/>
       <c r="BV37" s="6"/>
@@ -6678,39 +6695,39 @@
         <v>9829</v>
       </c>
       <c r="CQ37" s="3">
-        <f t="shared" ref="CQ37:CY37" si="46">+CP37</f>
+        <f t="shared" ref="CQ37:CY37" si="45">+CP37</f>
         <v>9829</v>
       </c>
       <c r="CR37" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>9829</v>
       </c>
       <c r="CS37" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>9829</v>
       </c>
       <c r="CT37" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>9829</v>
       </c>
       <c r="CU37" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>9829</v>
       </c>
       <c r="CV37" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>9829</v>
       </c>
       <c r="CW37" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>9829</v>
       </c>
       <c r="CX37" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>9829</v>
       </c>
       <c r="CY37" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>9829</v>
       </c>
     </row>
@@ -6723,47 +6740,47 @@
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6">
-        <f t="shared" ref="G38" si="47">SUM(G35:G37)</f>
+        <f t="shared" ref="G38" si="46">SUM(G35:G37)</f>
         <v>83</v>
       </c>
       <c r="H38" s="6">
-        <f t="shared" ref="H38" si="48">SUM(H35:H37)</f>
+        <f t="shared" ref="H38" si="47">SUM(H35:H37)</f>
         <v>102</v>
       </c>
       <c r="I38" s="6">
-        <f t="shared" ref="I38" si="49">SUM(I35:I37)</f>
+        <f t="shared" ref="I38" si="48">SUM(I35:I37)</f>
         <v>120</v>
       </c>
       <c r="J38" s="6">
-        <f t="shared" ref="J38:Q38" si="50">SUM(J35:J37)</f>
+        <f t="shared" ref="J38:Q38" si="49">SUM(J35:J37)</f>
         <v>144</v>
       </c>
       <c r="K38" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>176</v>
       </c>
       <c r="L38" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>278</v>
       </c>
       <c r="M38" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>304</v>
       </c>
       <c r="N38" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>336</v>
       </c>
       <c r="O38" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>400</v>
       </c>
       <c r="P38" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>1560</v>
       </c>
       <c r="Q38" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>563</v>
       </c>
       <c r="R38" s="6">
@@ -6791,67 +6808,67 @@
       <c r="AK38" s="6"/>
       <c r="AL38" s="6"/>
       <c r="AM38" s="6">
-        <f t="shared" ref="AM38:AN38" si="51">+AM37+AM36+AM35</f>
+        <f t="shared" ref="AM38:AN38" si="50">+AM37+AM36+AM35</f>
         <v>4590</v>
       </c>
       <c r="AN38" s="6">
+        <f t="shared" si="50"/>
+        <v>5154</v>
+      </c>
+      <c r="AO38" s="6">
+        <f t="shared" ref="AO38:AQ38" si="51">+AO37+AO36+AO35</f>
+        <v>5528</v>
+      </c>
+      <c r="AP38" s="6">
         <f t="shared" si="51"/>
-        <v>5154</v>
-      </c>
-      <c r="AO38" s="6">
-        <f t="shared" ref="AO38:AQ38" si="52">+AO37+AO36+AO35</f>
-        <v>5528</v>
-      </c>
-      <c r="AP38" s="6">
+        <v>6298</v>
+      </c>
+      <c r="AQ38" s="6">
+        <f t="shared" si="51"/>
+        <v>5944</v>
+      </c>
+      <c r="AR38" s="6">
+        <f t="shared" ref="AR38:AS38" si="52">+AR37+AR36+AR35</f>
+        <v>6953</v>
+      </c>
+      <c r="AS38" s="6">
         <f t="shared" si="52"/>
-        <v>6298</v>
-      </c>
-      <c r="AQ38" s="6">
-        <f t="shared" si="52"/>
-        <v>5944</v>
-      </c>
-      <c r="AR38" s="6">
-        <f t="shared" ref="AR38:AS38" si="53">+AR37+AR36+AR35</f>
-        <v>6953</v>
-      </c>
-      <c r="AS38" s="6">
+        <v>7312</v>
+      </c>
+      <c r="AT38" s="6">
+        <f t="shared" ref="AT38:AU38" si="53">+AT37+AT36+AT35</f>
+        <v>8732</v>
+      </c>
+      <c r="AU38" s="6">
         <f t="shared" si="53"/>
-        <v>7312</v>
-      </c>
-      <c r="AT38" s="6">
-        <f t="shared" ref="AT38:AU38" si="54">+AT37+AT36+AT35</f>
-        <v>8732</v>
-      </c>
-      <c r="AU38" s="6">
-        <f t="shared" si="54"/>
         <v>8385</v>
       </c>
       <c r="AV38" s="6">
-        <f t="shared" ref="AV38" si="55">+AV37+AV36+AV35</f>
+        <f t="shared" ref="AV38" si="54">+AV37+AV36+AV35</f>
         <v>8895</v>
       </c>
       <c r="AW38" s="6">
-        <f t="shared" ref="AW38" si="56">+AW37+AW36+AW35</f>
+        <f t="shared" ref="AW38" si="55">+AW37+AW36+AW35</f>
         <v>9236</v>
       </c>
       <c r="AX38" s="6">
-        <f t="shared" ref="AX38" si="57">+AX37+AX36+AX35</f>
+        <f t="shared" ref="AX38" si="56">+AX37+AX36+AX35</f>
         <v>10087</v>
       </c>
       <c r="AY38" s="6">
-        <f t="shared" ref="AY38:BB38" si="58">+AY37+AY36+AY35</f>
+        <f t="shared" ref="AY38:BB38" si="57">+AY37+AY36+AY35</f>
         <v>9662</v>
       </c>
       <c r="AZ38" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>11311</v>
       </c>
       <c r="BA38" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>12816</v>
       </c>
       <c r="BB38" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>14738</v>
       </c>
       <c r="BC38" s="6">
@@ -6859,31 +6876,31 @@
         <v>13379</v>
       </c>
       <c r="BD38" s="6">
-        <f t="shared" ref="BD38:BF38" si="59">+BD37+BD36+BD35</f>
+        <f t="shared" ref="BD38:BF38" si="58">+BD37+BD36+BD35</f>
         <v>15272</v>
       </c>
       <c r="BE38" s="6">
+        <f t="shared" si="58"/>
+        <v>16334</v>
+      </c>
+      <c r="BF38" s="6">
+        <f t="shared" si="58"/>
+        <v>17430</v>
+      </c>
+      <c r="BG38" s="6">
+        <f t="shared" ref="BG38:BJ38" si="59">+BG37+BG36+BG35</f>
+        <v>12041.1</v>
+      </c>
+      <c r="BH38" s="6">
         <f t="shared" si="59"/>
-        <v>16334</v>
-      </c>
-      <c r="BF38" s="6">
+        <v>14792</v>
+      </c>
+      <c r="BI38" s="6">
         <f t="shared" si="59"/>
-        <v>17430</v>
-      </c>
-      <c r="BG38" s="6">
-        <f t="shared" ref="BG38:BJ38" si="60">+BG37+BG36+BG35</f>
-        <v>12041.1</v>
-      </c>
-      <c r="BH38" s="6">
-        <f t="shared" si="60"/>
-        <v>14792</v>
-      </c>
-      <c r="BI38" s="6">
-        <f t="shared" si="60"/>
         <v>14188</v>
       </c>
       <c r="BJ38" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>16032</v>
       </c>
       <c r="BK38" s="6">
@@ -6907,64 +6924,67 @@
         <v>17187</v>
       </c>
       <c r="BP38" s="6">
-        <f t="shared" ref="BP38:BR38" si="61">+BP37+BP36+BP35</f>
+        <f t="shared" ref="BP38:BS38" si="60">+BP37+BP36+BP35</f>
         <v>18584</v>
       </c>
       <c r="BQ38" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>21501</v>
       </c>
       <c r="BR38" s="6">
-        <f t="shared" si="61"/>
-        <v>18932</v>
-      </c>
-      <c r="BS38" s="6"/>
+        <f t="shared" si="60"/>
+        <v>24243</v>
+      </c>
+      <c r="BS38" s="6">
+        <f t="shared" si="60"/>
+        <v>23221</v>
+      </c>
       <c r="BT38" s="6"/>
       <c r="BU38" s="6"/>
       <c r="BV38" s="6"/>
       <c r="BW38" s="6"/>
       <c r="CB38" s="6">
-        <f t="shared" ref="CB38:CC38" si="62">+CB37+CB36+CB35</f>
+        <f t="shared" ref="CB38:CC38" si="61">+CB37+CB36+CB35</f>
         <v>236</v>
       </c>
       <c r="CC38" s="6">
+        <f t="shared" si="61"/>
+        <v>203</v>
+      </c>
+      <c r="CD38" s="6">
+        <f t="shared" ref="CD38:CE38" si="62">+CD37+CD36+CD35</f>
+        <v>292</v>
+      </c>
+      <c r="CE38" s="6">
         <f t="shared" si="62"/>
-        <v>203</v>
-      </c>
-      <c r="CD38" s="6">
-        <f t="shared" ref="CD38:CE38" si="63">+CD37+CD36+CD35</f>
-        <v>292</v>
-      </c>
-      <c r="CE38" s="6">
+        <v>449</v>
+      </c>
+      <c r="CF38" s="6">
+        <f t="shared" ref="CF38:CG38" si="63">+CF37+CF36+CF35</f>
+        <v>1095</v>
+      </c>
+      <c r="CG38" s="6">
         <f t="shared" si="63"/>
-        <v>449</v>
-      </c>
-      <c r="CF38" s="6">
-        <f t="shared" ref="CF38:CG38" si="64">+CF37+CF36+CF35</f>
-        <v>1095</v>
-      </c>
-      <c r="CG38" s="6">
+        <v>3187</v>
+      </c>
+      <c r="CH38" s="6">
+        <f t="shared" ref="CH38:CL38" si="64">+CH37+CH36+CH35</f>
+        <v>3193</v>
+      </c>
+      <c r="CI38" s="6">
         <f t="shared" si="64"/>
-        <v>3187</v>
-      </c>
-      <c r="CH38" s="6">
-        <f t="shared" ref="CH38:CL38" si="65">+CH37+CH36+CH35</f>
-        <v>3193</v>
-      </c>
-      <c r="CI38" s="6">
-        <f t="shared" si="65"/>
         <v>5319</v>
       </c>
       <c r="CJ38" s="6">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>8836</v>
       </c>
       <c r="CK38" s="6">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>11422</v>
       </c>
       <c r="CL38" s="6">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>14996</v>
       </c>
       <c r="CM38" s="3">
@@ -6980,43 +7000,43 @@
         <v>36602</v>
       </c>
       <c r="CP38" s="3">
-        <f t="shared" ref="CP38" si="66">SUM(CP35:CP37)</f>
+        <f t="shared" ref="CP38" si="65">SUM(CP35:CP37)</f>
         <v>48527</v>
       </c>
       <c r="CQ38" s="3">
-        <f t="shared" ref="CQ38" si="67">SUM(CQ35:CQ37)</f>
+        <f t="shared" ref="CQ38" si="66">SUM(CQ35:CQ37)</f>
         <v>46061.5</v>
       </c>
       <c r="CR38" s="3">
-        <f t="shared" ref="CR38" si="68">SUM(CR35:CR37)</f>
+        <f t="shared" ref="CR38" si="67">SUM(CR35:CR37)</f>
         <v>43842.55</v>
       </c>
       <c r="CS38" s="3">
-        <f t="shared" ref="CS38" si="69">SUM(CS35:CS37)</f>
+        <f t="shared" ref="CS38" si="68">SUM(CS35:CS37)</f>
         <v>41845.494999999995</v>
       </c>
       <c r="CT38" s="3">
-        <f t="shared" ref="CT38" si="70">SUM(CT35:CT37)</f>
+        <f t="shared" ref="CT38" si="69">SUM(CT35:CT37)</f>
         <v>40048.145499999999</v>
       </c>
       <c r="CU38" s="3">
-        <f t="shared" ref="CU38" si="71">SUM(CU35:CU37)</f>
+        <f t="shared" ref="CU38" si="70">SUM(CU35:CU37)</f>
         <v>38430.53095</v>
       </c>
       <c r="CV38" s="3">
-        <f t="shared" ref="CV38" si="72">SUM(CV35:CV37)</f>
+        <f t="shared" ref="CV38" si="71">SUM(CV35:CV37)</f>
         <v>36974.677855000002</v>
       </c>
       <c r="CW38" s="3">
-        <f t="shared" ref="CW38" si="73">SUM(CW35:CW37)</f>
+        <f t="shared" ref="CW38" si="72">SUM(CW35:CW37)</f>
         <v>35664.410069499994</v>
       </c>
       <c r="CX38" s="3">
-        <f t="shared" ref="CX38" si="74">SUM(CX35:CX37)</f>
+        <f t="shared" ref="CX38" si="73">SUM(CX35:CX37)</f>
         <v>34485.169062549998</v>
       </c>
       <c r="CY38" s="3">
-        <f t="shared" ref="CY38" si="75">SUM(CY35:CY37)</f>
+        <f t="shared" ref="CY38" si="74">SUM(CY35:CY37)</f>
         <v>33423.852156294997</v>
       </c>
     </row>
@@ -7029,47 +7049,47 @@
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6">
-        <f t="shared" ref="G39" si="76">+G34-G38</f>
+        <f t="shared" ref="G39" si="75">+G34-G38</f>
         <v>162</v>
       </c>
       <c r="H39" s="6">
-        <f t="shared" ref="H39" si="77">+H34-H38</f>
+        <f t="shared" ref="H39" si="76">+H34-H38</f>
         <v>219</v>
       </c>
       <c r="I39" s="6">
-        <f t="shared" ref="I39" si="78">+I34-I38</f>
+        <f t="shared" ref="I39" si="77">+I34-I38</f>
         <v>216</v>
       </c>
       <c r="J39" s="6">
-        <f t="shared" ref="J39:Q39" si="79">+J34-J38</f>
+        <f t="shared" ref="J39:Q39" si="78">+J34-J38</f>
         <v>437</v>
       </c>
       <c r="K39" s="6">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>388</v>
       </c>
       <c r="L39" s="6">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>407</v>
       </c>
       <c r="M39" s="6">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>414</v>
       </c>
       <c r="N39" s="6">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>548</v>
       </c>
       <c r="O39" s="6">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>381</v>
       </c>
       <c r="P39" s="6">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>-743</v>
       </c>
       <c r="Q39" s="6">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>377</v>
       </c>
       <c r="R39" s="6">
@@ -7097,67 +7117,67 @@
       <c r="AK39" s="6"/>
       <c r="AL39" s="6"/>
       <c r="AM39" s="6">
-        <f t="shared" ref="AM39:AN39" si="80">+AM34-AM38</f>
+        <f t="shared" ref="AM39:AN39" si="79">+AM34-AM38</f>
         <v>5449</v>
       </c>
       <c r="AN39" s="6">
+        <f t="shared" si="79"/>
+        <v>5863</v>
+      </c>
+      <c r="AO39" s="6">
+        <f t="shared" ref="AO39:AQ39" si="80">+AO34-AO38</f>
+        <v>5781</v>
+      </c>
+      <c r="AP39" s="6">
         <f t="shared" si="80"/>
-        <v>5863</v>
-      </c>
-      <c r="AO39" s="6">
-        <f t="shared" ref="AO39:AQ39" si="81">+AO34-AO38</f>
-        <v>5781</v>
-      </c>
-      <c r="AP39" s="6">
+        <v>7820</v>
+      </c>
+      <c r="AQ39" s="6">
+        <f t="shared" si="80"/>
+        <v>6317</v>
+      </c>
+      <c r="AR39" s="6">
+        <f t="shared" ref="AR39:AS39" si="81">+AR34-AR38</f>
+        <v>6626</v>
+      </c>
+      <c r="AS39" s="6">
         <f t="shared" si="81"/>
-        <v>7820</v>
-      </c>
-      <c r="AQ39" s="6">
-        <f t="shared" si="81"/>
-        <v>6317</v>
-      </c>
-      <c r="AR39" s="6">
-        <f t="shared" ref="AR39:AS39" si="82">+AR34-AR38</f>
-        <v>6626</v>
-      </c>
-      <c r="AS39" s="6">
+        <v>7185</v>
+      </c>
+      <c r="AT39" s="6">
+        <f t="shared" ref="AT39:AU39" si="82">+AT34-AT38</f>
+        <v>8858</v>
+      </c>
+      <c r="AU39" s="6">
         <f t="shared" si="82"/>
-        <v>7185</v>
-      </c>
-      <c r="AT39" s="6">
-        <f t="shared" ref="AT39:AU39" si="83">+AT34-AT38</f>
-        <v>8858</v>
-      </c>
-      <c r="AU39" s="6">
-        <f t="shared" si="83"/>
         <v>5893</v>
       </c>
       <c r="AV39" s="6">
-        <f t="shared" ref="AV39" si="84">+AV34-AV38</f>
+        <f t="shared" ref="AV39" si="83">+AV34-AV38</f>
         <v>5963</v>
       </c>
       <c r="AW39" s="6">
-        <f t="shared" ref="AW39" si="85">+AW34-AW38</f>
+        <f t="shared" ref="AW39" si="84">+AW34-AW38</f>
         <v>8040</v>
       </c>
       <c r="AX39" s="6">
-        <f t="shared" ref="AX39" si="86">+AX34-AX38</f>
+        <f t="shared" ref="AX39" si="85">+AX34-AX38</f>
         <v>12775</v>
       </c>
       <c r="AY39" s="6">
-        <f t="shared" ref="AY39:BB39" si="87">+AY34-AY38</f>
+        <f t="shared" ref="AY39:BB39" si="86">+AY34-AY38</f>
         <v>11378</v>
       </c>
       <c r="AZ39" s="6">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>12367</v>
       </c>
       <c r="BA39" s="6">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>10423</v>
       </c>
       <c r="BB39" s="6">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>12585</v>
       </c>
       <c r="BC39" s="6">
@@ -7165,31 +7185,31 @@
         <v>8524</v>
       </c>
       <c r="BD39" s="6">
-        <f t="shared" ref="BD39:BF39" si="88">+BD34-BD38</f>
+        <f t="shared" ref="BD39:BF39" si="87">+BD34-BD38</f>
         <v>8358</v>
       </c>
       <c r="BE39" s="6">
+        <f t="shared" si="87"/>
+        <v>5664</v>
+      </c>
+      <c r="BF39" s="6">
+        <f t="shared" si="87"/>
+        <v>6399</v>
+      </c>
+      <c r="BG39" s="6">
+        <f t="shared" ref="BG39:BJ39" si="88">+BG34-BG38</f>
+        <v>10588.449999999999</v>
+      </c>
+      <c r="BH39" s="6">
         <f t="shared" si="88"/>
-        <v>5664</v>
-      </c>
-      <c r="BF39" s="6">
+        <v>11262</v>
+      </c>
+      <c r="BI39" s="6">
         <f t="shared" si="88"/>
-        <v>6399</v>
-      </c>
-      <c r="BG39" s="6">
-        <f t="shared" ref="BG39:BJ39" si="89">+BG34-BG38</f>
-        <v>10588.449999999999</v>
-      </c>
-      <c r="BH39" s="6">
-        <f t="shared" si="89"/>
-        <v>11262</v>
-      </c>
-      <c r="BI39" s="6">
-        <f t="shared" si="89"/>
         <v>13748</v>
       </c>
       <c r="BJ39" s="6">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>15655.690000000002</v>
       </c>
       <c r="BK39" s="6">
@@ -7213,64 +7233,67 @@
         <v>17555</v>
       </c>
       <c r="BP39" s="6">
-        <f t="shared" ref="BP39:BR39" si="90">+BP34-BP38</f>
+        <f t="shared" ref="BP39:BS39" si="89">+BP34-BP38</f>
         <v>20441</v>
       </c>
       <c r="BQ39" s="6">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>20535</v>
       </c>
       <c r="BR39" s="6">
-        <f t="shared" si="90"/>
-        <v>26046.696000000004</v>
-      </c>
-      <c r="BS39" s="6"/>
+        <f t="shared" si="89"/>
+        <v>24745</v>
+      </c>
+      <c r="BS39" s="6">
+        <f t="shared" si="89"/>
+        <v>23517.129999999997</v>
+      </c>
       <c r="BT39" s="6"/>
       <c r="BU39" s="6"/>
       <c r="BV39" s="6"/>
       <c r="BW39" s="6"/>
       <c r="CB39" s="6">
-        <f t="shared" ref="CB39:CC39" si="91">+CB34-CB38</f>
+        <f t="shared" ref="CB39:CC39" si="90">+CB34-CB38</f>
         <v>-124</v>
       </c>
       <c r="CC39" s="6">
+        <f t="shared" si="90"/>
+        <v>-55</v>
+      </c>
+      <c r="CD39" s="6">
+        <f t="shared" ref="CD39:CE39" si="91">+CD34-CD38</f>
+        <v>262</v>
+      </c>
+      <c r="CE39" s="6">
         <f t="shared" si="91"/>
-        <v>-55</v>
-      </c>
-      <c r="CD39" s="6">
-        <f t="shared" ref="CD39:CE39" si="92">+CD34-CD38</f>
-        <v>262</v>
-      </c>
-      <c r="CE39" s="6">
+        <v>1032</v>
+      </c>
+      <c r="CF39" s="6">
+        <f t="shared" ref="CF39:CG39" si="92">+CF34-CF38</f>
+        <v>1756</v>
+      </c>
+      <c r="CG39" s="6">
         <f t="shared" si="92"/>
-        <v>1032</v>
-      </c>
-      <c r="CF39" s="6">
-        <f t="shared" ref="CF39:CG39" si="93">+CF34-CF38</f>
-        <v>1756</v>
-      </c>
-      <c r="CG39" s="6">
+        <v>538</v>
+      </c>
+      <c r="CH39" s="6">
+        <f t="shared" ref="CH39:CL39" si="93">+CH34-CH38</f>
+        <v>2804</v>
+      </c>
+      <c r="CI39" s="6">
         <f t="shared" si="93"/>
-        <v>538</v>
-      </c>
-      <c r="CH39" s="6">
-        <f t="shared" ref="CH39:CL39" si="94">+CH34-CH38</f>
-        <v>2804</v>
-      </c>
-      <c r="CI39" s="6">
-        <f t="shared" si="94"/>
         <v>4994</v>
       </c>
       <c r="CJ39" s="6">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>6225</v>
       </c>
       <c r="CK39" s="6">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>12427</v>
       </c>
       <c r="CL39" s="6">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>20203</v>
       </c>
       <c r="CM39" s="3">
@@ -7286,44 +7309,44 @@
         <v>32671</v>
       </c>
       <c r="CP39" s="3">
-        <f t="shared" ref="CP39" si="95">CP34-CP38</f>
+        <f t="shared" ref="CP39" si="94">CP34-CP38</f>
         <v>46753</v>
       </c>
       <c r="CQ39" s="3">
-        <f t="shared" ref="CQ39" si="96">CQ34-CQ38</f>
+        <f t="shared" ref="CQ39" si="95">CQ34-CQ38</f>
         <v>48391.790000000008</v>
       </c>
       <c r="CR39" s="3">
-        <f t="shared" ref="CR39" si="97">CR34-CR38</f>
+        <f t="shared" ref="CR39" si="96">CR34-CR38</f>
         <v>65427.260000000009</v>
       </c>
       <c r="CS39" s="3">
-        <f t="shared" ref="CS39" si="98">CS34-CS38</f>
+        <f t="shared" ref="CS39" si="97">CS34-CS38</f>
         <v>91399.505000000005</v>
       </c>
       <c r="CT39" s="3">
-        <f t="shared" ref="CT39" si="99">CT34-CT38</f>
-        <v>118115.04650000001</v>
+        <f t="shared" ref="CT39" si="98">CT34-CT38</f>
+        <v>122733.50450000002</v>
       </c>
       <c r="CU39" s="3">
-        <f t="shared" ref="CU39" si="100">CU34-CU38</f>
-        <v>135548.98025000002</v>
+        <f t="shared" ref="CU39" si="99">CU34-CU38</f>
+        <v>140629.28405000002</v>
       </c>
       <c r="CV39" s="3">
-        <f t="shared" ref="CV39" si="101">CV34-CV38</f>
-        <v>150923.19424100005</v>
+        <f t="shared" ref="CV39" si="100">CV34-CV38</f>
+        <v>156409.92234500003</v>
       </c>
       <c r="CW39" s="3">
-        <f t="shared" ref="CW39" si="102">CW34-CW38</f>
-        <v>167265.29179418006</v>
+        <f t="shared" ref="CW39" si="101">CW34-CW38</f>
+        <v>173190.95814650005</v>
       </c>
       <c r="CX39" s="3">
-        <f t="shared" ref="CX39" si="103">CX34-CX38</f>
-        <v>178591.01789431408</v>
+        <f t="shared" ref="CX39" si="102">CX34-CX38</f>
+        <v>184812.96756425008</v>
       </c>
       <c r="CY39" s="3">
-        <f t="shared" ref="CY39" si="104">CY34-CY38</f>
-        <v>190306.14414841228</v>
+        <f t="shared" ref="CY39" si="103">CY34-CY38</f>
+        <v>196839.1913018451</v>
       </c>
     </row>
     <row r="40" spans="2:159" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7461,10 +7484,11 @@
         <v>1128</v>
       </c>
       <c r="BR40" s="6">
-        <f>+BQ40</f>
-        <v>1128</v>
-      </c>
-      <c r="BS40" s="6"/>
+        <v>609</v>
+      </c>
+      <c r="BS40" s="6">
+        <v>-1120</v>
+      </c>
       <c r="BT40" s="6"/>
       <c r="BU40" s="6"/>
       <c r="BV40" s="6"/>
@@ -7509,36 +7533,36 @@
         <v>531</v>
       </c>
       <c r="CR40" s="3">
-        <f t="shared" ref="CR40:CY40" si="105">+CQ59*$DD$58</f>
+        <f t="shared" ref="CR40:CY40" si="104">+CQ59*$DD$58</f>
         <v>938.78</v>
       </c>
       <c r="CS40" s="3">
-        <f t="shared" si="105"/>
+        <f t="shared" si="104"/>
         <v>2027.1830560000003</v>
       </c>
       <c r="CT40" s="3">
-        <f t="shared" si="105"/>
+        <f t="shared" si="104"/>
         <v>3559.3807401184004</v>
       </c>
       <c r="CU40" s="3">
-        <f t="shared" si="105"/>
-        <v>5554.8413468563422</v>
+        <f t="shared" si="104"/>
+        <v>5630.5840580563436</v>
       </c>
       <c r="CV40" s="3">
-        <f t="shared" si="105"/>
-        <v>7868.9440210447856</v>
+        <f t="shared" si="104"/>
+        <v>8029.2458950284681</v>
       </c>
       <c r="CW40" s="3">
-        <f t="shared" si="105"/>
-        <v>10473.13508854232</v>
+        <f t="shared" si="104"/>
+        <v>10726.048254164938</v>
       </c>
       <c r="CX40" s="3">
-        <f t="shared" si="105"/>
-        <v>13388.045289418968</v>
+        <f t="shared" si="104"/>
+        <v>13742.287159135842</v>
       </c>
       <c r="CY40" s="3">
-        <f t="shared" si="105"/>
-        <v>16536.50192563219</v>
+        <f t="shared" si="104"/>
+        <v>16998.593336599373</v>
       </c>
     </row>
     <row r="41" spans="2:159" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7582,67 +7606,67 @@
       <c r="AK41" s="6"/>
       <c r="AL41" s="6"/>
       <c r="AM41" s="6">
-        <f t="shared" ref="AM41:AN41" si="106">+AM39+AM40</f>
+        <f t="shared" ref="AM41:AN41" si="105">+AM39+AM40</f>
         <v>5610</v>
       </c>
       <c r="AN41" s="6">
+        <f t="shared" si="105"/>
+        <v>5868</v>
+      </c>
+      <c r="AO41" s="6">
+        <f t="shared" ref="AO41:AQ41" si="106">+AO39+AO40</f>
+        <v>5912</v>
+      </c>
+      <c r="AP41" s="6">
         <f t="shared" si="106"/>
-        <v>5868</v>
-      </c>
-      <c r="AO41" s="6">
-        <f t="shared" ref="AO41:AQ41" si="107">+AO39+AO40</f>
-        <v>5912</v>
-      </c>
-      <c r="AP41" s="6">
-        <f t="shared" si="107"/>
         <v>7971</v>
       </c>
       <c r="AQ41" s="6">
-        <f t="shared" si="107"/>
+        <f t="shared" si="106"/>
         <v>6523</v>
       </c>
       <c r="AR41" s="6">
-        <f t="shared" ref="AR41" si="108">+AR39+AR40</f>
+        <f t="shared" ref="AR41" si="107">+AR39+AR40</f>
         <v>6832</v>
       </c>
       <c r="AS41" s="6">
-        <f t="shared" ref="AS41:AT41" si="109">+AS39+AS40</f>
+        <f t="shared" ref="AS41:AT41" si="108">+AS39+AS40</f>
         <v>7329</v>
       </c>
       <c r="AT41" s="6">
+        <f t="shared" si="108"/>
+        <v>9169</v>
+      </c>
+      <c r="AU41" s="6">
+        <f t="shared" ref="AU41:BB41" si="109">+AU39+AU40</f>
+        <v>5861</v>
+      </c>
+      <c r="AV41" s="6">
         <f t="shared" si="109"/>
-        <v>9169</v>
-      </c>
-      <c r="AU41" s="6">
-        <f t="shared" ref="AU41:BB41" si="110">+AU39+AU40</f>
-        <v>5861</v>
-      </c>
-      <c r="AV41" s="6">
-        <f t="shared" si="110"/>
         <v>6131</v>
       </c>
       <c r="AW41" s="6">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>8133</v>
       </c>
       <c r="AX41" s="6">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>13055</v>
       </c>
       <c r="AY41" s="6">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>11503</v>
       </c>
       <c r="AZ41" s="6">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>12513</v>
       </c>
       <c r="BA41" s="6">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>10565</v>
       </c>
       <c r="BB41" s="6">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>12702</v>
       </c>
       <c r="BC41" s="6">
@@ -7650,31 +7674,31 @@
         <v>8908</v>
       </c>
       <c r="BD41" s="6">
-        <f t="shared" ref="BD41:BJ41" si="111">+BD39+BD40</f>
+        <f t="shared" ref="BD41:BJ41" si="110">+BD39+BD40</f>
         <v>8186</v>
       </c>
       <c r="BE41" s="6">
-        <f t="shared" si="111"/>
+        <f t="shared" si="110"/>
         <v>5576</v>
       </c>
       <c r="BF41" s="6">
-        <f t="shared" si="111"/>
+        <f t="shared" si="110"/>
         <v>6149</v>
       </c>
       <c r="BG41" s="6">
-        <f t="shared" si="111"/>
+        <f t="shared" si="110"/>
         <v>10338.449999999999</v>
       </c>
       <c r="BH41" s="6">
-        <f t="shared" si="111"/>
+        <f t="shared" si="110"/>
         <v>11163</v>
       </c>
       <c r="BI41" s="6">
-        <f t="shared" si="111"/>
+        <f t="shared" si="110"/>
         <v>14020</v>
       </c>
       <c r="BJ41" s="6">
-        <f t="shared" si="111"/>
+        <f t="shared" si="110"/>
         <v>16079.690000000002</v>
       </c>
       <c r="BK41" s="6">
@@ -7698,117 +7722,120 @@
         <v>18382</v>
       </c>
       <c r="BP41" s="6">
-        <f t="shared" ref="BP41:BR41" si="112">+BP39+BP40</f>
+        <f t="shared" ref="BP41:BS41" si="111">+BP39+BP40</f>
         <v>20534</v>
       </c>
       <c r="BQ41" s="6">
-        <f t="shared" si="112"/>
+        <f t="shared" si="111"/>
         <v>21663</v>
       </c>
       <c r="BR41" s="6">
-        <f t="shared" si="112"/>
-        <v>27174.696000000004</v>
-      </c>
-      <c r="BS41" s="6"/>
+        <f t="shared" si="111"/>
+        <v>25354</v>
+      </c>
+      <c r="BS41" s="6">
+        <f t="shared" si="111"/>
+        <v>22397.129999999997</v>
+      </c>
       <c r="BT41" s="6"/>
       <c r="BU41" s="6"/>
       <c r="BV41" s="6"/>
       <c r="BW41" s="6"/>
       <c r="CB41" s="3">
-        <f t="shared" ref="CB41" si="113">+CB39+CB40</f>
+        <f t="shared" ref="CB41" si="112">+CB39+CB40</f>
         <v>-124</v>
       </c>
       <c r="CC41" s="3">
-        <f t="shared" ref="CC41" si="114">+CC39+CC40</f>
+        <f t="shared" ref="CC41" si="113">+CC39+CC40</f>
         <v>-55</v>
       </c>
       <c r="CD41" s="3">
-        <f t="shared" ref="CD41" si="115">+CD39+CD40</f>
+        <f t="shared" ref="CD41" si="114">+CD39+CD40</f>
         <v>262</v>
       </c>
       <c r="CE41" s="3">
-        <f t="shared" ref="CE41:CO41" si="116">+CE39+CE40</f>
+        <f t="shared" ref="CE41:CO41" si="115">+CE39+CE40</f>
         <v>1008</v>
       </c>
       <c r="CF41" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="115"/>
         <v>1695</v>
       </c>
       <c r="CG41" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="115"/>
         <v>494</v>
       </c>
       <c r="CH41" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="115"/>
         <v>2754</v>
       </c>
       <c r="CI41" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="115"/>
         <v>4910</v>
       </c>
       <c r="CJ41" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="115"/>
         <v>6194</v>
       </c>
       <c r="CK41" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="115"/>
         <v>12518</v>
       </c>
       <c r="CL41" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="115"/>
         <v>20594</v>
       </c>
       <c r="CM41" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="115"/>
         <v>25361</v>
       </c>
       <c r="CN41" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="115"/>
         <v>29812</v>
       </c>
       <c r="CO41" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="115"/>
         <v>33180</v>
       </c>
       <c r="CP41" s="3">
-        <f t="shared" ref="CP41" si="117">+CP39+CP40</f>
+        <f t="shared" ref="CP41" si="116">+CP39+CP40</f>
         <v>47284</v>
       </c>
       <c r="CQ41" s="3">
-        <f t="shared" ref="CQ41" si="118">+CQ39+CQ40</f>
+        <f t="shared" ref="CQ41" si="117">+CQ39+CQ40</f>
         <v>48391.790000000008</v>
       </c>
       <c r="CR41" s="3">
-        <f t="shared" ref="CR41" si="119">+CR39+CR40</f>
+        <f t="shared" ref="CR41" si="118">+CR39+CR40</f>
         <v>66366.040000000008</v>
       </c>
       <c r="CS41" s="3">
-        <f t="shared" ref="CS41" si="120">+CS39+CS40</f>
+        <f t="shared" ref="CS41" si="119">+CS39+CS40</f>
         <v>93426.688055999999</v>
       </c>
       <c r="CT41" s="3">
-        <f t="shared" ref="CT41" si="121">+CT39+CT40</f>
-        <v>121674.42724011841</v>
+        <f t="shared" ref="CT41" si="120">+CT39+CT40</f>
+        <v>126292.88524011843</v>
       </c>
       <c r="CU41" s="3">
-        <f t="shared" ref="CU41" si="122">+CU39+CU40</f>
-        <v>141103.82159685637</v>
+        <f t="shared" ref="CU41" si="121">+CU39+CU40</f>
+        <v>146259.86810805637</v>
       </c>
       <c r="CV41" s="3">
-        <f t="shared" ref="CV41" si="123">+CV39+CV40</f>
-        <v>158792.13826204484</v>
+        <f t="shared" ref="CV41" si="122">+CV39+CV40</f>
+        <v>164439.16824002849</v>
       </c>
       <c r="CW41" s="3">
-        <f t="shared" ref="CW41" si="124">+CW39+CW40</f>
-        <v>177738.42688272239</v>
+        <f t="shared" ref="CW41" si="123">+CW39+CW40</f>
+        <v>183917.00640066498</v>
       </c>
       <c r="CX41" s="3">
-        <f t="shared" ref="CX41" si="125">+CX39+CX40</f>
-        <v>191979.06318373306</v>
+        <f t="shared" ref="CX41" si="124">+CX39+CX40</f>
+        <v>198555.25472338591</v>
       </c>
       <c r="CY41" s="3">
-        <f t="shared" ref="CY41" si="126">+CY39+CY40</f>
-        <v>206842.64607404446</v>
+        <f t="shared" ref="CY41" si="125">+CY39+CY40</f>
+        <v>213837.78463844449</v>
       </c>
     </row>
     <row r="42" spans="2:159" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7913,7 +7940,7 @@
         <v>1497</v>
       </c>
       <c r="BG42" s="6">
-        <f t="shared" ref="BG42" si="127">+BG41*0.19</f>
+        <f t="shared" ref="BG42" si="126">+BG41*0.19</f>
         <v>1964.3054999999997</v>
       </c>
       <c r="BH42" s="6">
@@ -7947,10 +7974,11 @@
         <v>0</v>
       </c>
       <c r="BR42" s="6">
-        <f>+BR41*0.15</f>
-        <v>4076.2044000000005</v>
-      </c>
-      <c r="BS42" s="6"/>
+        <v>2586</v>
+      </c>
+      <c r="BS42" s="6">
+        <v>0</v>
+      </c>
       <c r="BT42" s="6"/>
       <c r="BU42" s="6"/>
       <c r="BV42" s="6"/>
@@ -7997,36 +8025,36 @@
         <v>8710.5222000000012</v>
       </c>
       <c r="CR42" s="3">
-        <f t="shared" ref="CR42:CY42" si="128">+CR41*0.18</f>
+        <f t="shared" ref="CR42:CY42" si="127">+CR41*0.18</f>
         <v>11945.887200000001</v>
       </c>
       <c r="CS42" s="3">
-        <f t="shared" si="128"/>
+        <f t="shared" si="127"/>
         <v>16816.803850079999</v>
       </c>
       <c r="CT42" s="3">
-        <f t="shared" si="128"/>
-        <v>21901.396903221314</v>
+        <f t="shared" si="127"/>
+        <v>22732.719343221317</v>
       </c>
       <c r="CU42" s="3">
-        <f t="shared" si="128"/>
-        <v>25398.687887434146</v>
+        <f t="shared" si="127"/>
+        <v>26326.776259450144</v>
       </c>
       <c r="CV42" s="3">
-        <f t="shared" si="128"/>
-        <v>28582.584887168072</v>
+        <f t="shared" si="127"/>
+        <v>29599.050283205128</v>
       </c>
       <c r="CW42" s="3">
-        <f t="shared" si="128"/>
-        <v>31992.916838890029</v>
+        <f t="shared" si="127"/>
+        <v>33105.061152119692</v>
       </c>
       <c r="CX42" s="3">
-        <f t="shared" si="128"/>
-        <v>34556.231373071947</v>
+        <f t="shared" si="127"/>
+        <v>35739.945850209464</v>
       </c>
       <c r="CY42" s="3">
-        <f t="shared" si="128"/>
-        <v>37231.676293328004</v>
+        <f t="shared" si="127"/>
+        <v>38490.801234920007</v>
       </c>
     </row>
     <row r="43" spans="2:159" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8070,67 +8098,67 @@
       <c r="AK43" s="6"/>
       <c r="AL43" s="6"/>
       <c r="AM43" s="6">
-        <f t="shared" ref="AM43:AN43" si="129">+AM41-AM42</f>
+        <f t="shared" ref="AM43:AN43" si="128">+AM41-AM42</f>
         <v>4987</v>
       </c>
       <c r="AN43" s="6">
+        <f t="shared" si="128"/>
+        <v>5106</v>
+      </c>
+      <c r="AO43" s="6">
+        <f t="shared" ref="AO43:AQ43" si="129">+AO41-AO42</f>
+        <v>5137</v>
+      </c>
+      <c r="AP43" s="6">
         <f t="shared" si="129"/>
-        <v>5106</v>
-      </c>
-      <c r="AO43" s="6">
-        <f t="shared" ref="AO43:AQ43" si="130">+AO41-AO42</f>
-        <v>5137</v>
-      </c>
-      <c r="AP43" s="6">
-        <f t="shared" si="130"/>
         <v>6882</v>
       </c>
       <c r="AQ43" s="6">
-        <f t="shared" si="130"/>
+        <f t="shared" si="129"/>
         <v>4307</v>
       </c>
       <c r="AR43" s="6">
-        <f t="shared" ref="AR43" si="131">+AR41-AR42</f>
+        <f t="shared" ref="AR43" si="130">+AR41-AR42</f>
         <v>4616</v>
       </c>
       <c r="AS43" s="6">
-        <f t="shared" ref="AS43:AT43" si="132">+AS41-AS42</f>
+        <f t="shared" ref="AS43:AT43" si="131">+AS41-AS42</f>
         <v>6091</v>
       </c>
       <c r="AT43" s="6">
+        <f t="shared" si="131"/>
+        <v>7349</v>
+      </c>
+      <c r="AU43" s="6">
+        <f t="shared" ref="AU43:AV43" si="132">+AU41-AU42</f>
+        <v>4902</v>
+      </c>
+      <c r="AV43" s="6">
         <f t="shared" si="132"/>
-        <v>7349</v>
-      </c>
-      <c r="AU43" s="6">
-        <f t="shared" ref="AU43:AV43" si="133">+AU41-AU42</f>
-        <v>4902</v>
-      </c>
-      <c r="AV43" s="6">
+        <v>5178</v>
+      </c>
+      <c r="AW43" s="6">
+        <f t="shared" ref="AW43:BB43" si="133">+AW41-AW42</f>
+        <v>7846</v>
+      </c>
+      <c r="AX43" s="6">
         <f t="shared" si="133"/>
-        <v>5178</v>
-      </c>
-      <c r="AW43" s="6">
-        <f t="shared" ref="AW43:BB43" si="134">+AW41-AW42</f>
-        <v>7846</v>
-      </c>
-      <c r="AX43" s="6">
-        <f t="shared" si="134"/>
         <v>11219</v>
       </c>
       <c r="AY43" s="6">
-        <f t="shared" si="134"/>
+        <f t="shared" si="133"/>
         <v>9497</v>
       </c>
       <c r="AZ43" s="6">
-        <f t="shared" si="134"/>
+        <f t="shared" si="133"/>
         <v>10394</v>
       </c>
       <c r="BA43" s="6">
-        <f t="shared" si="134"/>
+        <f t="shared" si="133"/>
         <v>9194</v>
       </c>
       <c r="BB43" s="6">
-        <f t="shared" si="134"/>
+        <f t="shared" si="133"/>
         <v>10285</v>
       </c>
       <c r="BC43" s="6">
@@ -8138,389 +8166,392 @@
         <v>7465</v>
       </c>
       <c r="BD43" s="6">
-        <f t="shared" ref="BD43:BF43" si="135">+BD41-BD42</f>
+        <f t="shared" ref="BD43:BF43" si="134">+BD41-BD42</f>
         <v>6687</v>
       </c>
       <c r="BE43" s="6">
+        <f t="shared" si="134"/>
+        <v>4395</v>
+      </c>
+      <c r="BF43" s="6">
+        <f t="shared" si="134"/>
+        <v>4652</v>
+      </c>
+      <c r="BG43" s="6">
+        <f t="shared" ref="BG43:BS43" si="135">+BG41-BG42</f>
+        <v>8374.1444999999985</v>
+      </c>
+      <c r="BH43" s="6">
         <f t="shared" si="135"/>
-        <v>4395</v>
-      </c>
-      <c r="BF43" s="6">
+        <v>9658</v>
+      </c>
+      <c r="BI43" s="6">
         <f t="shared" si="135"/>
-        <v>4652</v>
-      </c>
-      <c r="BG43" s="6">
-        <f t="shared" ref="BG43:BR43" si="136">+BG41-BG42</f>
-        <v>8374.1444999999985</v>
-      </c>
-      <c r="BH43" s="6">
-        <f t="shared" si="136"/>
-        <v>9658</v>
-      </c>
-      <c r="BI43" s="6">
-        <f t="shared" si="136"/>
         <v>11583</v>
       </c>
       <c r="BJ43" s="6">
-        <f t="shared" si="136"/>
+        <f t="shared" si="135"/>
         <v>13288.690000000002</v>
       </c>
       <c r="BK43" s="6">
-        <f t="shared" si="136"/>
+        <f t="shared" si="135"/>
         <v>12369</v>
       </c>
       <c r="BL43" s="6">
-        <f t="shared" ref="BL43" si="137">+BL41-BL42</f>
+        <f t="shared" ref="BL43" si="136">+BL41-BL42</f>
         <v>13465</v>
       </c>
       <c r="BM43" s="6">
-        <f t="shared" si="136"/>
+        <f t="shared" si="135"/>
         <v>15688</v>
       </c>
       <c r="BN43" s="6">
-        <f t="shared" si="136"/>
+        <f t="shared" si="135"/>
         <v>20838</v>
       </c>
       <c r="BO43" s="6">
-        <f t="shared" si="136"/>
+        <f t="shared" si="135"/>
         <v>16644</v>
       </c>
       <c r="BP43" s="6">
-        <f t="shared" si="136"/>
+        <f t="shared" si="135"/>
         <v>18337</v>
       </c>
       <c r="BQ43" s="6">
-        <f t="shared" si="136"/>
+        <f t="shared" si="135"/>
         <v>21663</v>
       </c>
       <c r="BR43" s="6">
-        <f t="shared" si="136"/>
-        <v>23098.491600000001</v>
-      </c>
-      <c r="BS43" s="6"/>
+        <f t="shared" si="135"/>
+        <v>22768</v>
+      </c>
+      <c r="BS43" s="6">
+        <f t="shared" si="135"/>
+        <v>22397.129999999997</v>
+      </c>
       <c r="BT43" s="6"/>
       <c r="BU43" s="6"/>
       <c r="BV43" s="6"/>
       <c r="BW43" s="6"/>
       <c r="CB43" s="3">
-        <f t="shared" ref="CB43:CC43" si="138">+CB41-CB42</f>
+        <f t="shared" ref="CB43:CC43" si="137">+CB41-CB42</f>
         <v>-124</v>
       </c>
       <c r="CC43" s="3">
+        <f t="shared" si="137"/>
+        <v>-55</v>
+      </c>
+      <c r="CD43" s="3">
+        <f t="shared" ref="CD43:CO43" si="138">+CD41-CD42</f>
+        <v>262</v>
+      </c>
+      <c r="CE43" s="3">
         <f t="shared" si="138"/>
-        <v>-55</v>
-      </c>
-      <c r="CD43" s="3">
-        <f t="shared" ref="CD43:CO43" si="139">+CD41-CD42</f>
-        <v>262</v>
-      </c>
-      <c r="CE43" s="3">
-        <f t="shared" si="139"/>
         <v>606</v>
       </c>
       <c r="CF43" s="3">
-        <f t="shared" si="139"/>
+        <f t="shared" si="138"/>
         <v>1000</v>
       </c>
       <c r="CG43" s="3">
-        <f t="shared" si="139"/>
+        <f t="shared" si="138"/>
         <v>53</v>
       </c>
       <c r="CH43" s="3">
-        <f t="shared" si="139"/>
+        <f t="shared" si="138"/>
         <v>1500</v>
       </c>
       <c r="CI43" s="3">
-        <f t="shared" si="139"/>
+        <f t="shared" si="138"/>
         <v>2940</v>
       </c>
       <c r="CJ43" s="3">
-        <f t="shared" si="139"/>
+        <f t="shared" si="138"/>
         <v>3688</v>
       </c>
       <c r="CK43" s="3">
-        <f t="shared" si="139"/>
+        <f t="shared" si="138"/>
         <v>10217</v>
       </c>
       <c r="CL43" s="3">
-        <f t="shared" si="139"/>
+        <f t="shared" si="138"/>
         <v>15934</v>
       </c>
       <c r="CM43" s="3">
-        <f t="shared" si="139"/>
+        <f t="shared" si="138"/>
         <v>22111</v>
       </c>
       <c r="CN43" s="3">
-        <f t="shared" si="139"/>
+        <f t="shared" si="138"/>
         <v>23485</v>
       </c>
       <c r="CO43" s="3">
-        <f t="shared" si="139"/>
+        <f t="shared" si="138"/>
         <v>29146</v>
       </c>
       <c r="CP43" s="3">
-        <f t="shared" ref="CP43" si="140">+CP41-CP42</f>
+        <f t="shared" ref="CP43" si="139">+CP41-CP42</f>
         <v>39370</v>
       </c>
       <c r="CQ43" s="3">
-        <f t="shared" ref="CQ43" si="141">+CQ41-CQ42</f>
+        <f t="shared" ref="CQ43" si="140">+CQ41-CQ42</f>
         <v>39681.267800000009</v>
       </c>
       <c r="CR43" s="3">
-        <f t="shared" ref="CR43" si="142">+CR41-CR42</f>
+        <f t="shared" ref="CR43" si="141">+CR41-CR42</f>
         <v>54420.152800000011</v>
       </c>
       <c r="CS43" s="3">
-        <f t="shared" ref="CS43" si="143">+CS41-CS42</f>
+        <f t="shared" ref="CS43" si="142">+CS41-CS42</f>
         <v>76609.884205919996</v>
       </c>
       <c r="CT43" s="3">
-        <f t="shared" ref="CT43" si="144">+CT41-CT42</f>
-        <v>99773.030336897093</v>
+        <f t="shared" ref="CT43" si="143">+CT41-CT42</f>
+        <v>103560.16589689712</v>
       </c>
       <c r="CU43" s="3">
-        <f t="shared" ref="CU43" si="145">+CU41-CU42</f>
-        <v>115705.13370942223</v>
+        <f t="shared" ref="CU43" si="144">+CU41-CU42</f>
+        <v>119933.09184860623</v>
       </c>
       <c r="CV43" s="3">
-        <f t="shared" ref="CV43" si="146">+CV41-CV42</f>
-        <v>130209.55337487676</v>
+        <f t="shared" ref="CV43" si="145">+CV41-CV42</f>
+        <v>134840.11795682338</v>
       </c>
       <c r="CW43" s="3">
-        <f t="shared" ref="CW43" si="147">+CW41-CW42</f>
-        <v>145745.51004383236</v>
+        <f t="shared" ref="CW43" si="146">+CW41-CW42</f>
+        <v>150811.94524854529</v>
       </c>
       <c r="CX43" s="3">
-        <f t="shared" ref="CX43" si="148">+CX41-CX42</f>
-        <v>157422.83181066113</v>
+        <f t="shared" ref="CX43" si="147">+CX41-CX42</f>
+        <v>162815.30887317646</v>
       </c>
       <c r="CY43" s="3">
-        <f t="shared" ref="CY43" si="149">+CY41-CY42</f>
-        <v>169610.96978071646</v>
+        <f t="shared" ref="CY43" si="148">+CY41-CY42</f>
+        <v>175346.98340352447</v>
       </c>
       <c r="CZ43" s="3">
-        <f t="shared" ref="CZ43:EE43" si="150">+CY43*(1+$DD$57)</f>
-        <v>169610.96978071646</v>
+        <f t="shared" ref="CZ43:EE43" si="149">+CY43*(1+$DD$57)</f>
+        <v>175346.98340352447</v>
       </c>
       <c r="DA43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DB43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DC43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DD43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DE43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DF43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DG43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DH43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DI43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DJ43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DK43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DL43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DM43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DN43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DO43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DP43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DQ43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DR43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DS43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DT43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DU43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DV43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DW43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DX43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DY43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="DZ43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EA43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EB43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EC43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="ED43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EE43" s="3">
+        <f t="shared" si="149"/>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EF43" s="3">
+        <f t="shared" ref="EF43:FC43" si="150">+EE43*(1+$DD$57)</f>
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EG43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DB43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EH43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DC43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EI43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DD43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EJ43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DE43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EK43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DF43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EL43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DG43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EM43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DH43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EN43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DI43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EO43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DJ43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EP43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DK43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EQ43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DL43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="ER43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DM43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="ES43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DN43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="ET43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DO43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EU43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DP43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EV43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DQ43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EW43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DR43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EX43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DS43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EY43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DT43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="EZ43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DU43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="FA43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DV43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="FB43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DW43" s="3">
+        <v>175346.98340352447</v>
+      </c>
+      <c r="FC43" s="3">
         <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DX43" s="3">
-        <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DY43" s="3">
-        <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="DZ43" s="3">
-        <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EA43" s="3">
-        <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EB43" s="3">
-        <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EC43" s="3">
-        <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="ED43" s="3">
-        <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EE43" s="3">
-        <f t="shared" si="150"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EF43" s="3">
-        <f t="shared" ref="EF43:FC43" si="151">+EE43*(1+$DD$57)</f>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EG43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EH43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EI43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EJ43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EK43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EL43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EM43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EN43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EO43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EP43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EQ43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="ER43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="ES43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="ET43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EU43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EV43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EW43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EX43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EY43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="EZ43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="FA43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="FB43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
-      </c>
-      <c r="FC43" s="3">
-        <f t="shared" si="151"/>
-        <v>169610.96978071646</v>
+        <v>175346.98340352447</v>
       </c>
     </row>
     <row r="44" spans="2:159" x14ac:dyDescent="0.25">
@@ -8564,67 +8595,67 @@
       <c r="AK44" s="9"/>
       <c r="AL44" s="9"/>
       <c r="AM44" s="9">
-        <f t="shared" ref="AM44:AN44" si="152">+AM43/AM45</f>
+        <f t="shared" ref="AM44:AN44" si="151">+AM43/AM45</f>
         <v>1.6933786078098472</v>
       </c>
       <c r="AN44" s="9">
+        <f t="shared" si="151"/>
+        <v>1.7426621160409557</v>
+      </c>
+      <c r="AO44" s="9">
+        <f t="shared" ref="AO44:AQ44" si="152">+AO43/AO45</f>
+        <v>1.7634740817027119</v>
+      </c>
+      <c r="AP44" s="9">
         <f t="shared" si="152"/>
-        <v>1.7426621160409557</v>
-      </c>
-      <c r="AO44" s="9">
-        <f t="shared" ref="AO44:AQ44" si="153">+AO43/AO45</f>
-        <v>1.7634740817027119</v>
-      </c>
-      <c r="AP44" s="9">
-        <f t="shared" si="153"/>
         <v>2.3846153846153846</v>
       </c>
       <c r="AQ44" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="152"/>
         <v>1.4980869565217392</v>
       </c>
       <c r="AR44" s="9">
-        <f t="shared" ref="AR44" si="154">+AR43/AR45</f>
+        <f t="shared" ref="AR44" si="153">+AR43/AR45</f>
         <v>1.6055652173913044</v>
       </c>
       <c r="AS44" s="9">
-        <f t="shared" ref="AS44:AT44" si="155">+AS43/AS45</f>
+        <f t="shared" ref="AS44:AT44" si="154">+AS43/AS45</f>
         <v>2.1193458594293668</v>
       </c>
       <c r="AT44" s="9">
+        <f t="shared" si="154"/>
+        <v>2.559735283873215</v>
+      </c>
+      <c r="AU44" s="9">
+        <f t="shared" ref="AU44:AV44" si="155">+AU43/AU45</f>
+        <v>1.7092050209205021</v>
+      </c>
+      <c r="AV44" s="9">
         <f t="shared" si="155"/>
-        <v>2.559735283873215</v>
-      </c>
-      <c r="AU44" s="9">
-        <f t="shared" ref="AU44:AV44" si="156">+AU43/AU45</f>
-        <v>1.7092050209205021</v>
-      </c>
-      <c r="AV44" s="9">
+        <v>1.7985411601250434</v>
+      </c>
+      <c r="AW44" s="9">
+        <f t="shared" ref="AW44:BB44" si="156">+AW43/AW45</f>
+        <v>2.7139398132134209</v>
+      </c>
+      <c r="AX44" s="9">
         <f t="shared" si="156"/>
-        <v>1.7985411601250434</v>
-      </c>
-      <c r="AW44" s="9">
-        <f t="shared" ref="AW44:BB44" si="157">+AW43/AW45</f>
-        <v>2.7139398132134209</v>
-      </c>
-      <c r="AX44" s="9">
-        <f t="shared" si="157"/>
         <v>3.882006920415225</v>
       </c>
       <c r="AY44" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="156"/>
         <v>3.2952810548230396</v>
       </c>
       <c r="AZ44" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="156"/>
         <v>3.6127911018421965</v>
       </c>
       <c r="BA44" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="156"/>
         <v>3.2158097236796084</v>
       </c>
       <c r="BB44" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="156"/>
         <v>3.6745266166488033</v>
       </c>
       <c r="BC44" s="9">
@@ -8632,154 +8663,157 @@
         <v>2.7224653537563821</v>
       </c>
       <c r="BD44" s="9">
-        <f t="shared" ref="BD44:BF44" si="158">+BD43/BD45</f>
+        <f t="shared" ref="BD44:BF44" si="157">+BD43/BD45</f>
         <v>2.4647991153704387</v>
       </c>
       <c r="BE44" s="9">
+        <f t="shared" si="157"/>
+        <v>1.6356531447711202</v>
+      </c>
+      <c r="BF44" s="9">
+        <f t="shared" si="157"/>
+        <v>1.7621212121212122</v>
+      </c>
+      <c r="BG44" s="9">
+        <f t="shared" ref="BG44:BS44" si="158">+BG43/BG45</f>
+        <v>3.1720244318181812</v>
+      </c>
+      <c r="BH44" s="9">
         <f t="shared" si="158"/>
-        <v>1.6356531447711202</v>
-      </c>
-      <c r="BF44" s="9">
+        <v>3.6975497702909648</v>
+      </c>
+      <c r="BI44" s="9">
         <f t="shared" si="158"/>
-        <v>1.7621212121212122</v>
-      </c>
-      <c r="BG44" s="9">
-        <f t="shared" ref="BG44:BR44" si="159">+BG43/BG45</f>
-        <v>3.1720244318181812</v>
-      </c>
-      <c r="BH44" s="9">
-        <f t="shared" si="159"/>
-        <v>3.6975497702909648</v>
-      </c>
-      <c r="BI44" s="9">
-        <f t="shared" si="159"/>
         <v>4.3858386974630825</v>
       </c>
       <c r="BJ44" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="158"/>
         <v>5.0527338403041835</v>
       </c>
       <c r="BK44" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="158"/>
         <v>4.7119999999999997</v>
       </c>
       <c r="BL44" s="9">
-        <f t="shared" ref="BL44" si="160">+BL43/BL45</f>
+        <f t="shared" ref="BL44" si="159">+BL43/BL45</f>
         <v>5.1590038314176248</v>
       </c>
       <c r="BM44" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="158"/>
         <v>6.0338461538461541</v>
       </c>
       <c r="BN44" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="158"/>
         <v>8.0176991150442483</v>
       </c>
       <c r="BO44" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="158"/>
         <v>6.4262548262548265</v>
       </c>
       <c r="BP44" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="158"/>
         <v>7.1350194552529187</v>
       </c>
       <c r="BQ44" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="158"/>
         <v>8.422628304821151</v>
       </c>
       <c r="BR44" s="9">
-        <f t="shared" si="159"/>
-        <v>8.9807510108864701</v>
-      </c>
-      <c r="BS44" s="9"/>
+        <f t="shared" si="158"/>
+        <v>8.8764132553606245</v>
+      </c>
+      <c r="BS44" s="9">
+        <f t="shared" si="158"/>
+        <v>8.7352301092043678</v>
+      </c>
       <c r="BT44" s="9"/>
       <c r="BU44" s="9"/>
       <c r="BV44" s="9"/>
       <c r="BW44" s="9"/>
       <c r="CD44" s="17"/>
       <c r="CE44" s="17">
-        <f t="shared" ref="CE44:CO44" si="161">+CE43/CE45</f>
+        <f t="shared" ref="CE44:CO44" si="160">+CE43/CE45</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="CF44" s="17">
-        <f t="shared" si="161"/>
+        <f t="shared" si="160"/>
         <v>0.66312997347480107</v>
       </c>
       <c r="CG44" s="17">
-        <f t="shared" si="161"/>
+        <f t="shared" si="160"/>
         <v>2.4469067405355493E-2</v>
       </c>
       <c r="CH44" s="17">
-        <f t="shared" si="161"/>
+        <f t="shared" si="160"/>
         <v>0.59594755661501786</v>
       </c>
       <c r="CI44" s="17">
-        <f t="shared" si="161"/>
+        <f t="shared" si="160"/>
         <v>1.1036036036036037</v>
       </c>
       <c r="CJ44" s="17">
-        <f t="shared" si="161"/>
+        <f t="shared" si="160"/>
         <v>1.2926743778478795</v>
       </c>
       <c r="CK44" s="17">
-        <f t="shared" si="161"/>
+        <f t="shared" si="160"/>
         <v>3.4929914529914532</v>
       </c>
       <c r="CL44" s="17">
-        <f t="shared" si="161"/>
+        <f t="shared" si="160"/>
         <v>5.4850243863516397</v>
       </c>
       <c r="CM44" s="17">
-        <f t="shared" si="161"/>
+        <f t="shared" si="160"/>
         <v>7.5696679219445393</v>
       </c>
       <c r="CN44" s="17">
-        <f t="shared" si="161"/>
+        <f t="shared" si="160"/>
         <v>8.1658553546592483</v>
       </c>
       <c r="CO44" s="17">
-        <f t="shared" si="161"/>
+        <f t="shared" si="160"/>
         <v>10.092105263157896</v>
       </c>
       <c r="CP44" s="17">
-        <f t="shared" ref="CP44" si="162">+CP43/CP45</f>
+        <f t="shared" ref="CP44" si="161">+CP43/CP45</f>
         <v>13.770549143057012</v>
       </c>
       <c r="CQ44" s="17">
-        <f t="shared" ref="CQ44" si="163">+CQ43/CQ45</f>
+        <f t="shared" ref="CQ44" si="162">+CQ43/CQ45</f>
         <v>14.721301354108704</v>
       </c>
       <c r="CR44" s="17">
-        <f t="shared" ref="CR44" si="164">+CR43/CR45</f>
+        <f t="shared" ref="CR44" si="163">+CR43/CR45</f>
         <v>20.189260916342057</v>
       </c>
       <c r="CS44" s="17">
-        <f t="shared" ref="CS44" si="165">+CS43/CS45</f>
+        <f t="shared" ref="CS44" si="164">+CS43/CS45</f>
         <v>29.369324978309372</v>
       </c>
       <c r="CT44" s="17">
-        <f t="shared" ref="CT44" si="166">+CT43/CT45</f>
-        <v>38.249196985584469</v>
+        <f t="shared" ref="CT44" si="165">+CT43/CT45</f>
+        <v>39.701041171898453</v>
       </c>
       <c r="CU44" s="17">
-        <f t="shared" ref="CU44" si="167">+CU43/CU45</f>
-        <v>44.356961360713903</v>
+        <f t="shared" ref="CU44" si="166">+CU43/CU45</f>
+        <v>45.977800210314825</v>
       </c>
       <c r="CV44" s="17">
-        <f t="shared" ref="CV44" si="168">+CV43/CV45</f>
-        <v>49.917405932481032</v>
+        <f t="shared" ref="CV44" si="167">+CV43/CV45</f>
+        <v>51.692588827611033</v>
       </c>
       <c r="CW44" s="17">
-        <f t="shared" ref="CW44" si="169">+CW43/CW45</f>
-        <v>55.873302681170159</v>
+        <f t="shared" ref="CW44" si="168">+CW43/CW45</f>
+        <v>57.815581847247572</v>
       </c>
       <c r="CX44" s="17">
-        <f t="shared" ref="CX44" si="170">+CX43/CX45</f>
-        <v>60.349945106636426</v>
+        <f t="shared" ref="CX44" si="169">+CX43/CX45</f>
+        <v>62.417216359277923</v>
       </c>
       <c r="CY44" s="17">
-        <f t="shared" ref="CY44" si="171">+CY43/CY45</f>
-        <v>65.022415097073591</v>
+        <f t="shared" ref="CY44" si="170">+CY43/CY45</f>
+        <v>67.221385241910852</v>
       </c>
     </row>
     <row r="45" spans="2:159" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8917,10 +8951,11 @@
         <v>2572</v>
       </c>
       <c r="BR45" s="6">
-        <f>+BQ45</f>
-        <v>2572</v>
-      </c>
-      <c r="BS45" s="6"/>
+        <v>2565</v>
+      </c>
+      <c r="BS45" s="6">
+        <v>2564</v>
+      </c>
       <c r="BT45" s="6"/>
       <c r="BU45" s="6"/>
       <c r="BV45" s="6"/>
@@ -8967,7 +9002,7 @@
         <v>2695.5</v>
       </c>
       <c r="CR45" s="3">
-        <f t="shared" ref="CR45:CY45" si="172">+CQ45</f>
+        <f t="shared" ref="CR45:CY45" si="171">+CQ45</f>
         <v>2695.5</v>
       </c>
       <c r="CS45" s="3">
@@ -8975,27 +9010,27 @@
         <v>2608.5</v>
       </c>
       <c r="CT45" s="3">
-        <f t="shared" si="172"/>
+        <f t="shared" si="171"/>
         <v>2608.5</v>
       </c>
       <c r="CU45" s="3">
-        <f t="shared" si="172"/>
+        <f t="shared" si="171"/>
         <v>2608.5</v>
       </c>
       <c r="CV45" s="3">
-        <f t="shared" si="172"/>
+        <f t="shared" si="171"/>
         <v>2608.5</v>
       </c>
       <c r="CW45" s="3">
-        <f t="shared" si="172"/>
+        <f t="shared" si="171"/>
         <v>2608.5</v>
       </c>
       <c r="CX45" s="3">
-        <f t="shared" si="172"/>
+        <f t="shared" si="171"/>
         <v>2608.5</v>
       </c>
       <c r="CY45" s="3">
-        <f t="shared" si="172"/>
+        <f t="shared" si="171"/>
         <v>2608.5</v>
       </c>
     </row>
@@ -9047,23 +9082,23 @@
       <c r="AO47" s="12"/>
       <c r="AP47" s="12"/>
       <c r="AQ47" s="11">
-        <f t="shared" ref="AQ47:AU47" si="173">+AQ32/AM32-1</f>
+        <f t="shared" ref="AQ47:AU47" si="172">+AQ32/AM32-1</f>
         <v>0.25998662878154777</v>
       </c>
       <c r="AR47" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="172"/>
         <v>0.2762451817700855</v>
       </c>
       <c r="AS47" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="172"/>
         <v>0.2859328331026445</v>
       </c>
       <c r="AT47" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="172"/>
         <v>0.2464230814709707</v>
       </c>
       <c r="AU47" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="172"/>
         <v>0.17642767128739134</v>
       </c>
       <c r="AV47" s="11">
@@ -9087,11 +9122,11 @@
         <v>0.5560014983678494</v>
       </c>
       <c r="BA47" s="11">
-        <f t="shared" ref="BA47:BB47" si="174">+BA32/AW32-1</f>
+        <f t="shared" ref="BA47:BB47" si="173">+BA32/AW32-1</f>
         <v>0.35118770377270603</v>
       </c>
       <c r="BB47" s="11">
-        <f t="shared" si="174"/>
+        <f t="shared" si="173"/>
         <v>0.19945141065830718</v>
       </c>
       <c r="BC47" s="11">
@@ -9107,7 +9142,7 @@
         <v>-4.4674250258531556E-2</v>
       </c>
       <c r="BF47" s="11">
-        <f t="shared" ref="BF47" si="175">+BF32/BB32-1</f>
+        <f t="shared" ref="BF47" si="174">+BF32/BB32-1</f>
         <v>-4.4726916337501144E-2</v>
       </c>
       <c r="BG47" s="11">
@@ -9115,31 +9150,31 @@
         <v>2.6408198366060009E-2</v>
       </c>
       <c r="BH47" s="11">
-        <f t="shared" ref="BH47" si="176">+BH32/BD32-1</f>
+        <f t="shared" ref="BH47" si="175">+BH32/BD32-1</f>
         <v>0.11022829782804799</v>
       </c>
       <c r="BI47" s="11">
-        <f t="shared" ref="BI47" si="177">+BI32/BE32-1</f>
+        <f t="shared" ref="BI47" si="176">+BI32/BE32-1</f>
         <v>0.23208486685429741</v>
       </c>
       <c r="BJ47" s="11">
-        <f t="shared" ref="BJ47" si="178">+BJ32/BF32-1</f>
+        <f t="shared" ref="BJ47" si="177">+BJ32/BF32-1</f>
         <v>0.24703870666873939</v>
       </c>
       <c r="BK47" s="11">
-        <f t="shared" ref="BK47:BR47" si="179">+BK32/BG32-1</f>
+        <f t="shared" ref="BK47:BS47" si="178">+BK32/BG32-1</f>
         <v>0.27264793157619138</v>
       </c>
       <c r="BL47" s="11">
-        <f t="shared" si="179"/>
+        <f t="shared" si="178"/>
         <v>0.2210069064658271</v>
       </c>
       <c r="BM47" s="11">
-        <f t="shared" si="179"/>
+        <f t="shared" si="178"/>
         <v>0.18868974404029748</v>
       </c>
       <c r="BN47" s="11">
-        <f t="shared" si="179"/>
+        <f t="shared" si="178"/>
         <v>0.20627757971628724</v>
       </c>
       <c r="BO47" s="11">
@@ -9147,76 +9182,79 @@
         <v>0.16071869428062002</v>
       </c>
       <c r="BP47" s="11">
-        <f t="shared" si="179"/>
+        <f t="shared" si="178"/>
         <v>0.21614496685521223</v>
       </c>
       <c r="BQ47" s="11">
-        <f t="shared" si="179"/>
+        <f t="shared" si="178"/>
         <v>0.26246027248761972</v>
       </c>
       <c r="BR47" s="11">
-        <f t="shared" si="179"/>
-        <v>0.12000000000000011</v>
-      </c>
-      <c r="BS47" s="11"/>
+        <f t="shared" si="178"/>
+        <v>0.23784230649994842</v>
+      </c>
+      <c r="BS47" s="11">
+        <f t="shared" si="178"/>
+        <v>0.33078886420570019</v>
+      </c>
       <c r="BT47" s="11"/>
       <c r="BU47" s="11"/>
       <c r="BV47" s="11"/>
       <c r="BW47" s="11"/>
       <c r="BZ47" s="18">
-        <f t="shared" ref="BZ47:CL47" si="180">+BZ32/BY32-1</f>
+        <f t="shared" ref="BZ47:CL47" si="179">+BZ32/BY32-1</f>
         <v>22.560209424083769</v>
       </c>
       <c r="CA47" s="18">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>4.333333333333333</v>
       </c>
       <c r="CB47" s="18">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>2.1875</v>
       </c>
       <c r="CC47" s="18">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>0.77777777777777768</v>
       </c>
       <c r="CD47" s="18">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>1.8566176470588234</v>
       </c>
       <c r="CE47" s="18">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>1.5405405405405403</v>
       </c>
       <c r="CF47" s="18">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>0.87993920972644379</v>
       </c>
       <c r="CG47" s="18">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>0.37132848288870934</v>
       </c>
       <c r="CH47" s="18">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>0.5468657889565729</v>
       </c>
       <c r="CI47" s="18">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>0.58358739837398366</v>
       </c>
       <c r="CJ47" s="18">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>0.43815177282207607</v>
       </c>
       <c r="CK47" s="18">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>0.54161088799643009</v>
       </c>
       <c r="CL47" s="18">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>0.47090961719371882</v>
       </c>
       <c r="CM47" s="18">
-        <f t="shared" ref="CM47" si="181">+CM32/CL32-1</f>
+        <f t="shared" ref="CM47" si="180">+CM32/CL32-1</f>
         <v>0.37352716896661997</v>
       </c>
       <c r="CN47" s="18">
@@ -9236,35 +9274,35 @@
         <v>-1.1193175554782941E-2</v>
       </c>
       <c r="CR47" s="18">
-        <f t="shared" ref="CR47:CY47" si="182">+CR32/CQ32-1</f>
+        <f t="shared" ref="CR47:CY47" si="181">+CR32/CQ32-1</f>
         <v>0.15686610810486323</v>
       </c>
       <c r="CS47" s="18">
-        <f t="shared" si="182"/>
+        <f t="shared" si="181"/>
         <v>0.21941275453851339</v>
       </c>
       <c r="CT47" s="18">
-        <f t="shared" si="182"/>
-        <v>0.1870103343465046</v>
+        <f t="shared" si="181"/>
+        <v>0.22167173252279637</v>
       </c>
       <c r="CU47" s="18">
-        <f t="shared" si="182"/>
+        <f t="shared" si="181"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="CV47" s="18">
-        <f t="shared" si="182"/>
+        <f t="shared" si="181"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="CW47" s="18">
-        <f t="shared" si="182"/>
+        <f t="shared" si="181"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="CX47" s="18">
-        <f t="shared" si="182"/>
+        <f t="shared" si="181"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="CY47" s="18">
-        <f t="shared" si="182"/>
+        <f t="shared" si="181"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -9325,15 +9363,15 @@
         <v>0.41985917173887088</v>
       </c>
       <c r="AZ48" s="11">
-        <f t="shared" ref="AZ48:BB48" si="183">+AZ27/AV27-1</f>
+        <f t="shared" ref="AZ48:BB48" si="182">+AZ27/AV27-1</f>
         <v>0.47543879015343848</v>
       </c>
       <c r="BA48" s="11">
-        <f t="shared" si="183"/>
+        <f t="shared" si="182"/>
         <v>0.31097316780136164</v>
       </c>
       <c r="BB48" s="11">
-        <f t="shared" si="183"/>
+        <f t="shared" si="182"/>
         <v>0.14539923954372624</v>
       </c>
       <c r="BC48" s="11">
@@ -9345,7 +9383,7 @@
         <v>-1</v>
       </c>
       <c r="BE48" s="11">
-        <f t="shared" ref="BE48" si="184">+BE27/BA27-1</f>
+        <f t="shared" ref="BE48" si="183">+BE27/BA27-1</f>
         <v>-1</v>
       </c>
       <c r="BF48" s="11"/>
@@ -9551,71 +9589,71 @@
       <c r="AZ51" s="10"/>
       <c r="BA51" s="10"/>
       <c r="BB51" s="10">
-        <f t="shared" ref="BB51" si="185">+BB30/AX30-1</f>
+        <f t="shared" ref="BB51" si="184">+BB30/AX30-1</f>
         <v>0.22315202231520215</v>
       </c>
       <c r="BC51" s="10">
-        <f t="shared" ref="BC51:BK51" si="186">+BC30/AY30-1</f>
+        <f t="shared" ref="BC51:BK51" si="185">+BC30/AY30-1</f>
         <v>0.30149812734082393</v>
       </c>
       <c r="BD51" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="185"/>
         <v>0.4819672131147541</v>
       </c>
       <c r="BE51" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="185"/>
         <v>-0.489247311827957</v>
       </c>
       <c r="BF51" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="185"/>
         <v>-0.17103762827822122</v>
       </c>
       <c r="BG51" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="185"/>
         <v>-0.51223021582733819</v>
       </c>
       <c r="BH51" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="185"/>
         <v>-0.38938053097345138</v>
       </c>
       <c r="BI51" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="185"/>
         <v>-0.26315789473684215</v>
       </c>
       <c r="BJ51" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="185"/>
         <v>0.47317744154057761</v>
       </c>
       <c r="BK51" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="185"/>
         <v>0.29793510324483785</v>
       </c>
       <c r="BL51" s="10">
-        <f t="shared" ref="BL51" si="187">+BL30/BH30-1</f>
+        <f t="shared" ref="BL51" si="186">+BL30/BH30-1</f>
         <v>0.27898550724637672</v>
       </c>
       <c r="BM51" s="10">
-        <f t="shared" ref="BM51" si="188">+BM30/BI30-1</f>
+        <f t="shared" ref="BM51" si="187">+BM30/BI30-1</f>
         <v>0.28571428571428581</v>
       </c>
       <c r="BN51" s="10">
-        <f t="shared" ref="BN51" si="189">+BN30/BJ30-1</f>
+        <f t="shared" ref="BN51" si="188">+BN30/BJ30-1</f>
         <v>1.1204481792717047E-2</v>
       </c>
       <c r="BO51" s="10">
-        <f t="shared" ref="BO51" si="190">+BO30/BK30-1</f>
+        <f t="shared" ref="BO51" si="189">+BO30/BK30-1</f>
         <v>-6.3636363636363602E-2</v>
       </c>
       <c r="BP51" s="10">
-        <f t="shared" ref="BP51" si="191">+BP30/BL30-1</f>
+        <f t="shared" ref="BP51" si="190">+BP30/BL30-1</f>
         <v>4.8158640226628968E-2</v>
       </c>
       <c r="BQ51" s="10">
-        <f t="shared" ref="BQ51" si="192">+BQ30/BM30-1</f>
+        <f t="shared" ref="BQ51" si="191">+BQ30/BM30-1</f>
         <v>-1</v>
       </c>
       <c r="BR51" s="10">
-        <f t="shared" ref="BR51" si="193">+BR30/BN30-1</f>
+        <f t="shared" ref="BR51" si="192">+BR30/BN30-1</f>
         <v>-1</v>
       </c>
       <c r="BS51" s="10"/>
@@ -9624,7 +9662,7 @@
       <c r="BV51" s="10"/>
       <c r="BW51" s="10"/>
       <c r="CO51" s="19">
-        <f t="shared" ref="CO51" si="194">CO30/CN30-1</f>
+        <f t="shared" ref="CO51" si="193">CO30/CN30-1</f>
         <v>1.2734530938123751</v>
       </c>
       <c r="CP51" s="19">
@@ -9691,19 +9729,19 @@
       <c r="AY52" s="6"/>
       <c r="AZ52" s="6"/>
       <c r="BA52" s="10">
-        <f t="shared" ref="BA52:BD52" si="195">+BA38/AW38-1</f>
+        <f t="shared" ref="BA52:BD52" si="194">+BA38/AW38-1</f>
         <v>0.38761368557817244</v>
       </c>
       <c r="BB52" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="194"/>
         <v>0.46108852979081982</v>
       </c>
       <c r="BC52" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="194"/>
         <v>0.38470296004967919</v>
       </c>
       <c r="BD52" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="194"/>
         <v>0.35019008045265676</v>
       </c>
       <c r="BE52" s="10">
@@ -9711,23 +9749,23 @@
         <v>0.27450062421972543</v>
       </c>
       <c r="BF52" s="10">
-        <f t="shared" ref="BF52:BJ52" si="196">+BF38/BB38-1</f>
+        <f t="shared" ref="BF52:BJ52" si="195">+BF38/BB38-1</f>
         <v>0.18265707694395439</v>
       </c>
       <c r="BG52" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="195"/>
         <v>-9.9999999999999978E-2</v>
       </c>
       <c r="BH52" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="195"/>
         <v>-3.1430068098480923E-2</v>
       </c>
       <c r="BI52" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="195"/>
         <v>-0.13138239255540585</v>
       </c>
       <c r="BJ52" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="195"/>
         <v>-8.0206540447504304E-2</v>
       </c>
       <c r="BK52" s="10">
@@ -9735,32 +9773,32 @@
         <v>0.32853310744035014</v>
       </c>
       <c r="BL52" s="10">
-        <f t="shared" ref="BL52:BO52" si="197">+BL38/BH38-1</f>
+        <f t="shared" ref="BL52:BO52" si="196">+BL38/BH38-1</f>
         <v>0.14359113034072468</v>
       </c>
       <c r="BM52" s="10">
-        <f t="shared" si="197"/>
+        <f t="shared" si="196"/>
         <v>0.11812799548914565</v>
       </c>
       <c r="BN52" s="10">
-        <f t="shared" si="197"/>
+        <f t="shared" si="196"/>
         <v>9.2939121756487886E-3</v>
       </c>
       <c r="BO52" s="10">
-        <f t="shared" si="197"/>
+        <f t="shared" si="196"/>
         <v>7.4388947927736426E-2</v>
       </c>
       <c r="BP52" s="10">
-        <f t="shared" ref="BP52" si="198">+BP38/BL38-1</f>
+        <f t="shared" ref="BP52" si="197">+BP38/BL38-1</f>
         <v>9.8604871127926152E-2</v>
       </c>
       <c r="BQ52" s="10">
-        <f t="shared" ref="BQ52" si="199">+BQ38/BM38-1</f>
+        <f t="shared" ref="BQ52" si="198">+BQ38/BM38-1</f>
         <v>0.35533282904689867</v>
       </c>
       <c r="BR52" s="10">
-        <f t="shared" ref="BR52" si="200">+BR38/BN38-1</f>
-        <v>0.17001421420184171</v>
+        <f t="shared" ref="BR52" si="199">+BR38/BN38-1</f>
+        <v>0.49823867498918495</v>
       </c>
       <c r="BS52" s="10"/>
       <c r="BT52" s="10"/>
@@ -9884,99 +9922,99 @@
       <c r="AK54" s="10"/>
       <c r="AL54" s="10"/>
       <c r="AM54" s="10">
-        <f t="shared" ref="AM54:BJ54" si="201">+AM34/AM32</f>
+        <f t="shared" ref="AM54:BJ54" si="200">+AM34/AM32</f>
         <v>0.8389603877653351</v>
       </c>
       <c r="AN54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.83266570931902351</v>
       </c>
       <c r="AO54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.82385080498288044</v>
       </c>
       <c r="AP54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.83469315360056762</v>
       </c>
       <c r="AQ54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.81322544272733299</v>
       </c>
       <c r="AR54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.80415729006277392</v>
       </c>
       <c r="AS54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.82126671198731027</v>
       </c>
       <c r="AT54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.83436106631249407</v>
       </c>
       <c r="AU54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.80498393189378137</v>
       </c>
       <c r="AV54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.7950981966072671</v>
       </c>
       <c r="AW54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.80465766185374943</v>
       </c>
       <c r="AX54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.81440581362211462</v>
       </c>
       <c r="AY54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.80394329601467274</v>
       </c>
       <c r="AZ54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.81432059703545756</v>
       </c>
       <c r="BA54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.80106859703550504</v>
       </c>
       <c r="BB54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.81146981081642955</v>
       </c>
       <c r="BC54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.78482872294682526</v>
       </c>
       <c r="BD54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.81985982929706469</v>
       </c>
       <c r="BE54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.79375045103557773</v>
       </c>
       <c r="BF54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.74083631276231932</v>
       </c>
       <c r="BG54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.78999999999999992</v>
       </c>
       <c r="BH54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.81421294415450485</v>
       </c>
       <c r="BI54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.81813389562467054</v>
       </c>
       <c r="BJ54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>0.79</v>
       </c>
       <c r="BK54" s="10">
@@ -9984,34 +10022,37 @@
         <v>0.81785763269784661</v>
       </c>
       <c r="BL54" s="10">
-        <f t="shared" ref="BL54:BO54" si="202">+BL34/BL32</f>
+        <f t="shared" ref="BL54:BO54" si="201">+BL34/BL32</f>
         <v>0.81295590079598679</v>
       </c>
       <c r="BM54" s="10">
+        <f t="shared" si="201"/>
+        <v>0.81830052477272164</v>
+      </c>
+      <c r="BN54" s="10">
+        <f t="shared" si="201"/>
+        <v>0.81731941717474421</v>
+      </c>
+      <c r="BO54" s="10">
+        <f t="shared" si="201"/>
+        <v>0.82105213404546962</v>
+      </c>
+      <c r="BP54" s="10">
+        <f t="shared" ref="BP54:BR54" si="202">+BP34/BP32</f>
+        <v>0.82130229817324696</v>
+      </c>
+      <c r="BQ54" s="10">
         <f t="shared" si="202"/>
-        <v>0.81830052477272164</v>
-      </c>
-      <c r="BN54" s="10">
+        <v>0.82034268763904605</v>
+      </c>
+      <c r="BR54" s="10">
         <f t="shared" si="202"/>
-        <v>0.81731941717474421</v>
-      </c>
-      <c r="BO54" s="10">
-        <f t="shared" si="202"/>
-        <v>0.82105213404546962</v>
-      </c>
-      <c r="BP54" s="10">
-        <f t="shared" ref="BP54:BR54" si="203">+BP34/BP32</f>
-        <v>0.82130229817324696</v>
-      </c>
-      <c r="BQ54" s="10">
-        <f t="shared" si="203"/>
-        <v>0.82034268763904605</v>
-      </c>
-      <c r="BR54" s="10">
-        <f t="shared" si="203"/>
+        <v>0.8179253001185447</v>
+      </c>
+      <c r="BS54" s="10">
+        <f t="shared" ref="BS54" si="203">+BS34/BS32</f>
         <v>0.83</v>
       </c>
-      <c r="BS54" s="10"/>
       <c r="BT54" s="10"/>
       <c r="BU54" s="10"/>
       <c r="BV54" s="10"/>
@@ -10046,7 +10087,7 @@
       </c>
       <c r="CT54" s="19">
         <f t="shared" si="204"/>
-        <v>0.81</v>
+        <v>0.81000000000000016</v>
       </c>
       <c r="CU54" s="19">
         <f t="shared" si="204"/>
@@ -10235,71 +10276,74 @@
       </c>
       <c r="BR55" s="10">
         <f t="shared" si="212"/>
-        <v>0.48064438506621004</v>
-      </c>
-      <c r="BS55" s="10"/>
+        <v>0.41315345699831368</v>
+      </c>
+      <c r="BS55" s="10">
+        <f t="shared" ref="BS55" si="213">+BS39/BS32</f>
+        <v>0.41762941521194791</v>
+      </c>
       <c r="BT55" s="10"/>
       <c r="BU55" s="10"/>
       <c r="BV55" s="10"/>
       <c r="BW55" s="10"/>
       <c r="CM55" s="10">
-        <f t="shared" ref="CM55:CY55" si="213">+CM39/CM32</f>
+        <f t="shared" ref="CM55:CY55" si="214">+CM39/CM32</f>
         <v>0.44616569361366809</v>
       </c>
       <c r="CN55" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>0.41000325332050863</v>
       </c>
       <c r="CO55" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>0.3800500203571221</v>
       </c>
       <c r="CP55" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>0.39645040660058173</v>
       </c>
       <c r="CQ55" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>0.4149918959943058</v>
       </c>
       <c r="CR55" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>0.48500203853196056</v>
       </c>
       <c r="CS55" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>0.55562009118541034</v>
       </c>
       <c r="CT55" s="10">
-        <f t="shared" si="213"/>
-        <v>0.60490172495380601</v>
+        <f t="shared" si="214"/>
+        <v>0.61072079466573792</v>
       </c>
       <c r="CU55" s="10">
-        <f t="shared" si="213"/>
-        <v>0.63107818412183248</v>
+        <f t="shared" si="214"/>
+        <v>0.63615457259631369</v>
       </c>
       <c r="CV55" s="10">
-        <f t="shared" si="213"/>
-        <v>0.65060761982845494</v>
+        <f t="shared" si="214"/>
+        <v>0.65512991711038016</v>
       </c>
       <c r="CW55" s="10">
-        <f t="shared" si="213"/>
-        <v>0.66764443602395429</v>
+        <f t="shared" si="214"/>
+        <v>0.67168336297480946</v>
       </c>
       <c r="CX55" s="10">
-        <f t="shared" si="213"/>
-        <v>0.67890610659219108</v>
+        <f t="shared" si="214"/>
+        <v>0.68262551624776613</v>
       </c>
       <c r="CY55" s="10">
-        <f t="shared" si="213"/>
-        <v>0.68899110224930837</v>
+        <f t="shared" si="214"/>
+        <v>0.69242437935325629</v>
       </c>
       <c r="DC55" t="s">
         <v>112</v>
       </c>
       <c r="DD55" s="3">
         <f>NPV(DD56,CR43:FC43)</f>
-        <v>1774326.4429682596</v>
+        <v>1831247.0110735227</v>
       </c>
     </row>
     <row r="56" spans="2:108" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -10343,99 +10387,99 @@
       <c r="AK56" s="10"/>
       <c r="AL56" s="10"/>
       <c r="AM56" s="10">
-        <f t="shared" ref="AM56:BF56" si="214">+AM42/AM41</f>
+        <f t="shared" ref="AM56:BF56" si="215">+AM42/AM41</f>
         <v>0.11105169340463458</v>
       </c>
       <c r="AN56" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.12985685071574643</v>
       </c>
       <c r="AO56" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.13108930987821379</v>
       </c>
       <c r="AP56" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.13662024840045164</v>
       </c>
       <c r="AQ56" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.33972098727579336</v>
       </c>
       <c r="AR56" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.32435597189695553</v>
       </c>
       <c r="AS56" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.16891799699822621</v>
       </c>
       <c r="AT56" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.19849492856363835</v>
       </c>
       <c r="AU56" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.16362395495649207</v>
       </c>
       <c r="AV56" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.15543956940140272</v>
       </c>
       <c r="AW56" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>3.5288331488995447E-2</v>
       </c>
       <c r="AX56" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.14063577173496744</v>
       </c>
       <c r="AY56" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.17438928975049986</v>
       </c>
       <c r="AZ56" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.16934388236234316</v>
       </c>
       <c r="BA56" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.12976810222432561</v>
       </c>
       <c r="BB56" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.19028499448905684</v>
       </c>
       <c r="BC56" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.1619892231701841</v>
       </c>
       <c r="BD56" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.18311751771316884</v>
       </c>
       <c r="BE56" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.21180057388809181</v>
       </c>
       <c r="BF56" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.24345422019840623</v>
       </c>
       <c r="BG56" s="10">
-        <f t="shared" ref="BG56:BJ56" si="215">+BG42/BG41</f>
+        <f t="shared" ref="BG56:BJ56" si="216">+BG42/BG41</f>
         <v>0.19</v>
       </c>
       <c r="BH56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>0.13482038878437697</v>
       </c>
       <c r="BI56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>0.1738231098430813</v>
       </c>
       <c r="BJ56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>0.17357299798690146</v>
       </c>
       <c r="BK56" s="10">
@@ -10443,88 +10487,91 @@
         <v>0.12789959811041388</v>
       </c>
       <c r="BL56" s="10">
-        <f t="shared" ref="BL56:BO56" si="216">+BL42/BL41</f>
+        <f t="shared" ref="BL56:BO56" si="217">+BL42/BL41</f>
         <v>0.10863233152389778</v>
       </c>
       <c r="BM56" s="10">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>0.11973964762652901</v>
       </c>
       <c r="BN56" s="10">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>0.11527193988027003</v>
       </c>
       <c r="BO56" s="10">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>9.4549015341094556E-2</v>
       </c>
       <c r="BP56" s="10">
-        <f t="shared" ref="BP56:BR56" si="217">+BP42/BP41</f>
+        <f t="shared" ref="BP56:BR56" si="218">+BP42/BP41</f>
         <v>0.10699327943897925</v>
       </c>
       <c r="BQ56" s="10">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>0</v>
       </c>
       <c r="BR56" s="10">
-        <f t="shared" si="217"/>
-        <v>0.15</v>
-      </c>
-      <c r="BS56" s="10"/>
+        <f t="shared" si="218"/>
+        <v>0.10199574031710973</v>
+      </c>
+      <c r="BS56" s="10">
+        <f t="shared" ref="BS56" si="219">+BS42/BS41</f>
+        <v>0</v>
+      </c>
       <c r="BT56" s="10"/>
       <c r="BU56" s="10"/>
       <c r="BV56" s="10"/>
       <c r="BW56" s="10"/>
       <c r="CM56" s="19">
-        <f t="shared" ref="CM56:CY56" si="218">+CM42/CM41</f>
+        <f t="shared" ref="CM56:CY56" si="220">+CM42/CM41</f>
         <v>0.12814952091794488</v>
       </c>
       <c r="CN56" s="19">
-        <f t="shared" si="218"/>
+        <f t="shared" si="220"/>
         <v>0.21222997450690997</v>
       </c>
       <c r="CO56" s="19">
-        <f t="shared" si="218"/>
+        <f t="shared" si="220"/>
         <v>0.12157926461723931</v>
       </c>
       <c r="CP56" s="19">
-        <f t="shared" si="218"/>
+        <f t="shared" si="220"/>
         <v>0.16737162676592504</v>
       </c>
       <c r="CQ56" s="19">
-        <f t="shared" si="218"/>
+        <f t="shared" si="220"/>
         <v>0.18</v>
       </c>
       <c r="CR56" s="19">
-        <f t="shared" si="218"/>
+        <f t="shared" si="220"/>
         <v>0.18</v>
       </c>
       <c r="CS56" s="19">
-        <f t="shared" si="218"/>
+        <f t="shared" si="220"/>
         <v>0.18</v>
       </c>
       <c r="CT56" s="19">
-        <f t="shared" si="218"/>
+        <f t="shared" si="220"/>
         <v>0.18</v>
       </c>
       <c r="CU56" s="19">
-        <f t="shared" si="218"/>
+        <f t="shared" si="220"/>
         <v>0.18</v>
       </c>
       <c r="CV56" s="19">
-        <f t="shared" si="218"/>
+        <f t="shared" si="220"/>
         <v>0.18</v>
       </c>
       <c r="CW56" s="19">
-        <f t="shared" si="218"/>
+        <f t="shared" si="220"/>
+        <v>0.17999999999999997</v>
+      </c>
+      <c r="CX56" s="19">
+        <f t="shared" si="220"/>
         <v>0.18</v>
       </c>
-      <c r="CX56" s="19">
-        <f t="shared" si="218"/>
-        <v>0.18</v>
-      </c>
       <c r="CY56" s="19">
-        <f t="shared" si="218"/>
+        <f t="shared" si="220"/>
         <v>0.18</v>
       </c>
       <c r="DC56" s="3" t="s">
@@ -10548,75 +10595,81 @@
         <v>195</v>
       </c>
       <c r="BA58" s="6">
-        <f t="shared" ref="BA58:BC58" si="219">+BA59-BA73</f>
+        <f t="shared" ref="BA58:BC58" si="221">+BA59-BA73</f>
         <v>64833</v>
       </c>
       <c r="BB58" s="6">
-        <f t="shared" si="219"/>
+        <f t="shared" si="221"/>
         <v>54773</v>
       </c>
       <c r="BC58" s="6">
-        <f t="shared" si="219"/>
+        <f t="shared" si="221"/>
         <v>50665</v>
       </c>
       <c r="BD58" s="6">
-        <f t="shared" ref="BD58:BG58" si="220">+BD59-BD73</f>
+        <f t="shared" ref="BD58:BG58" si="222">+BD59-BD73</f>
         <v>47025</v>
       </c>
       <c r="BE58" s="6">
-        <f t="shared" si="220"/>
+        <f t="shared" si="222"/>
         <v>38382</v>
       </c>
       <c r="BF58" s="6">
-        <f t="shared" si="220"/>
+        <f t="shared" si="222"/>
         <v>37016</v>
       </c>
       <c r="BG58" s="6">
-        <f t="shared" si="220"/>
+        <f t="shared" si="222"/>
         <v>33681</v>
       </c>
       <c r="BH58" s="6">
-        <f t="shared" ref="BH58:BQ58" si="221">+BH59-BH73</f>
+        <f t="shared" ref="BH58:BS58" si="223">+BH59-BH73</f>
         <v>41272</v>
       </c>
       <c r="BI58" s="6">
-        <f t="shared" si="221"/>
+        <f t="shared" si="223"/>
         <v>48882</v>
       </c>
       <c r="BJ58" s="6">
-        <f t="shared" si="221"/>
+        <f t="shared" si="223"/>
         <v>53159</v>
       </c>
       <c r="BK58" s="6">
-        <f t="shared" si="221"/>
+        <f t="shared" si="223"/>
         <v>45951</v>
       </c>
       <c r="BL58" s="6">
-        <f t="shared" si="221"/>
+        <f t="shared" si="223"/>
         <v>45898</v>
       </c>
       <c r="BM58" s="6">
-        <f t="shared" si="221"/>
+        <f t="shared" si="223"/>
         <v>48148</v>
       </c>
       <c r="BN58" s="6">
-        <f t="shared" si="221"/>
+        <f t="shared" si="223"/>
         <v>55059</v>
       </c>
       <c r="BO58" s="6">
-        <f t="shared" si="221"/>
+        <f t="shared" si="223"/>
         <v>47569</v>
       </c>
       <c r="BP58" s="6">
-        <f t="shared" si="221"/>
+        <f t="shared" si="223"/>
         <v>40227</v>
       </c>
       <c r="BQ58" s="6">
-        <f t="shared" si="221"/>
+        <f t="shared" si="223"/>
         <v>40688</v>
       </c>
-      <c r="BR58" s="6"/>
-      <c r="BS58" s="6"/>
+      <c r="BR58" s="6">
+        <f t="shared" si="223"/>
+        <v>0</v>
+      </c>
+      <c r="BS58" s="6">
+        <f t="shared" si="223"/>
+        <v>50842</v>
+      </c>
       <c r="BT58" s="6"/>
       <c r="BU58" s="6"/>
       <c r="BV58" s="6"/>
@@ -10760,7 +10813,10 @@
         <v>69522</v>
       </c>
       <c r="BR59" s="6"/>
-      <c r="BS59" s="6"/>
+      <c r="BS59" s="6">
+        <f>23426+57754+28410</f>
+        <v>109590</v>
+      </c>
       <c r="BT59" s="6"/>
       <c r="BU59" s="6"/>
       <c r="BV59" s="6"/>
@@ -10774,43 +10830,43 @@
         <v>46939</v>
       </c>
       <c r="CR59" s="3">
-        <f t="shared" ref="CR59:CY59" si="222">+CQ59+CR43</f>
+        <f t="shared" ref="CR59:CY59" si="224">+CQ59+CR43</f>
         <v>101359.15280000001</v>
       </c>
       <c r="CS59" s="3">
-        <f t="shared" si="222"/>
+        <f t="shared" si="224"/>
         <v>177969.03700592002</v>
       </c>
       <c r="CT59" s="3">
-        <f t="shared" si="222"/>
-        <v>277742.06734281708</v>
+        <f t="shared" si="224"/>
+        <v>281529.20290281717</v>
       </c>
       <c r="CU59" s="3">
-        <f t="shared" si="222"/>
-        <v>393447.20105223928</v>
+        <f t="shared" si="224"/>
+        <v>401462.29475142341</v>
       </c>
       <c r="CV59" s="3">
-        <f t="shared" si="222"/>
-        <v>523656.75442711601</v>
+        <f t="shared" si="224"/>
+        <v>536302.41270824685</v>
       </c>
       <c r="CW59" s="3">
-        <f t="shared" si="222"/>
-        <v>669402.26447094837</v>
+        <f t="shared" si="224"/>
+        <v>687114.35795679211</v>
       </c>
       <c r="CX59" s="3">
-        <f t="shared" si="222"/>
-        <v>826825.0962816095</v>
+        <f t="shared" si="224"/>
+        <v>849929.66682996857</v>
       </c>
       <c r="CY59" s="3">
-        <f t="shared" si="222"/>
-        <v>996436.06606232596</v>
+        <f t="shared" si="224"/>
+        <v>1025276.6502334931</v>
       </c>
       <c r="DC59" s="3" t="s">
         <v>115</v>
       </c>
       <c r="DD59" s="17">
         <f>DD55/Main!M3</f>
-        <v>689.86253614629061</v>
+        <v>714.21490291479051</v>
       </c>
     </row>
     <row r="60" spans="2:108" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -10924,12 +10980,15 @@
       <c r="BQ60" s="3">
         <v>17297</v>
       </c>
+      <c r="BS60" s="3">
+        <v>17470</v>
+      </c>
       <c r="DC60" s="3" t="s">
         <v>116</v>
       </c>
       <c r="DD60" s="19">
         <f>DD59/Main!M2-1</f>
-        <v>1.3014003151675002E-2</v>
+        <v>0.1805205006856041</v>
       </c>
     </row>
     <row r="61" spans="2:108" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -11043,6 +11102,9 @@
       <c r="BQ61" s="3">
         <v>11373</v>
       </c>
+      <c r="BS61" s="3">
+        <v>11115</v>
+      </c>
     </row>
     <row r="62" spans="2:108" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B62" s="3" t="s">
@@ -11155,6 +11217,9 @@
       <c r="BQ62" s="3">
         <v>160270</v>
       </c>
+      <c r="BS62" s="3">
+        <v>194776</v>
+      </c>
     </row>
     <row r="63" spans="2:108" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B63" s="3" t="s">
@@ -11266,6 +11331,9 @@
       </c>
       <c r="BQ63" s="3">
         <v>17372</v>
+      </c>
+      <c r="BS63" s="3">
+        <v>23268</v>
       </c>
     </row>
     <row r="64" spans="2:108" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -11392,6 +11460,9 @@
       <c r="BQ64" s="3">
         <v>21158</v>
       </c>
+      <c r="BS64" s="3">
+        <v>24748</v>
+      </c>
     </row>
     <row r="65" spans="2:75" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B65" s="3" t="s">
@@ -11504,6 +11575,9 @@
       <c r="BQ65" s="3">
         <v>6852</v>
       </c>
+      <c r="BS65" s="3">
+        <v>14283</v>
+      </c>
     </row>
     <row r="66" spans="2:75" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="3" t="s">
@@ -11557,23 +11631,23 @@
       <c r="AV66" s="6"/>
       <c r="AW66" s="6"/>
       <c r="AX66" s="6">
-        <f t="shared" ref="AX66:AY66" si="223">SUM(AX59:AX65)</f>
+        <f t="shared" ref="AX66:AY66" si="225">SUM(AX59:AX65)</f>
         <v>159316</v>
       </c>
       <c r="AY66" s="6">
-        <f t="shared" si="223"/>
+        <f t="shared" si="225"/>
         <v>163523</v>
       </c>
       <c r="AZ66" s="6">
-        <f t="shared" ref="AZ66:BA66" si="224">SUM(AZ59:AZ65)</f>
+        <f t="shared" ref="AZ66:BA66" si="226">SUM(AZ59:AZ65)</f>
         <v>170609</v>
       </c>
       <c r="BA66" s="6">
-        <f t="shared" si="224"/>
+        <f t="shared" si="226"/>
         <v>169585</v>
       </c>
       <c r="BB66" s="6">
-        <f t="shared" ref="BB66" si="225">SUM(BB59:BB65)</f>
+        <f t="shared" ref="BB66" si="227">SUM(BB59:BB65)</f>
         <v>165987</v>
       </c>
       <c r="BC66" s="6">
@@ -11589,52 +11663,60 @@
         <v>178894</v>
       </c>
       <c r="BF66" s="6">
-        <f t="shared" ref="BF66:BQ66" si="226">SUM(BF59:BF65)</f>
+        <f t="shared" ref="BF66:BS66" si="228">SUM(BF59:BF65)</f>
         <v>185727</v>
       </c>
       <c r="BG66" s="6">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>184491</v>
       </c>
       <c r="BH66" s="6">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>206688</v>
       </c>
       <c r="BI66" s="6">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>216274</v>
       </c>
       <c r="BJ66" s="6">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>229623</v>
       </c>
       <c r="BK66" s="6">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>222844</v>
       </c>
       <c r="BL66" s="6">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>230238</v>
       </c>
       <c r="BM66" s="6">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>256408</v>
       </c>
       <c r="BN66" s="6">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>276054</v>
       </c>
       <c r="BO66" s="6">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>280213</v>
       </c>
       <c r="BP66" s="6">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>294744</v>
       </c>
       <c r="BQ66" s="6">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>303844</v>
+      </c>
+      <c r="BR66" s="6">
+        <f t="shared" si="228"/>
+        <v>0</v>
+      </c>
+      <c r="BS66" s="6">
+        <f t="shared" si="228"/>
+        <v>395250</v>
       </c>
     </row>
     <row r="67" spans="2:75" x14ac:dyDescent="0.25">
@@ -11704,6 +11786,9 @@
       <c r="BQ68" s="3">
         <v>7798</v>
       </c>
+      <c r="BS68" s="3">
+        <v>13326</v>
+      </c>
     </row>
     <row r="69" spans="2:75" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
@@ -11769,6 +11854,9 @@
       <c r="BQ69" s="3">
         <v>0</v>
       </c>
+      <c r="BS69" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" spans="2:75" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
@@ -11854,6 +11942,10 @@
         <f>2113+20113</f>
         <v>22226</v>
       </c>
+      <c r="BS70" s="3">
+        <f>2414+25607</f>
+        <v>28021</v>
+      </c>
     </row>
     <row r="71" spans="2:75" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
@@ -11918,6 +12010,9 @@
       </c>
       <c r="BQ71" s="3">
         <v>27047</v>
+      </c>
+      <c r="BS71" s="3">
+        <v>31013</v>
       </c>
     </row>
     <row r="72" spans="2:75" x14ac:dyDescent="0.25">
@@ -11975,6 +12070,9 @@
       </c>
       <c r="BQ72" s="3">
         <v>11738</v>
+      </c>
+      <c r="BS72" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="2:75" x14ac:dyDescent="0.25">
@@ -12028,7 +12126,9 @@
         <v>28834</v>
       </c>
       <c r="BR73" s="6"/>
-      <c r="BS73" s="6"/>
+      <c r="BS73" s="6">
+        <v>58748</v>
+      </c>
       <c r="BT73" s="6"/>
       <c r="BU73" s="6"/>
       <c r="BV73" s="6"/>
@@ -12104,6 +12204,10 @@
       <c r="BQ74" s="3">
         <v>12135</v>
       </c>
+      <c r="BS74" s="3">
+        <f>3612+16849</f>
+        <v>20461</v>
+      </c>
     </row>
     <row r="75" spans="2:75" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
@@ -12169,6 +12273,9 @@
       <c r="BQ75" s="3">
         <v>92330</v>
       </c>
+      <c r="BS75" s="3">
+        <v>99337</v>
+      </c>
     </row>
     <row r="76" spans="2:75" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
@@ -12234,6 +12341,9 @@
       <c r="BQ76" s="3">
         <v>159</v>
       </c>
+      <c r="BS76" s="3">
+        <v>-303</v>
+      </c>
     </row>
     <row r="77" spans="2:75" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
@@ -12299,41 +12409,44 @@
       <c r="BQ77" s="3">
         <v>101577</v>
       </c>
+      <c r="BS77" s="3">
+        <v>144647</v>
+      </c>
     </row>
     <row r="78" spans="2:75" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
         <v>61</v>
       </c>
       <c r="AX78" s="6">
-        <f t="shared" ref="AX78:AY78" si="227">SUM(AX68:AX77)</f>
+        <f t="shared" ref="AX78:AY78" si="229">SUM(AX68:AX77)</f>
         <v>159316</v>
       </c>
       <c r="AY78" s="6">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>163523</v>
       </c>
       <c r="AZ78" s="6">
-        <f t="shared" ref="AZ78:BA78" si="228">SUM(AZ68:AZ77)</f>
+        <f t="shared" ref="AZ78:BA78" si="230">SUM(AZ68:AZ77)</f>
         <v>170609</v>
       </c>
       <c r="BA78" s="6">
-        <f t="shared" si="228"/>
+        <f t="shared" si="230"/>
         <v>169585</v>
       </c>
       <c r="BB78" s="6">
-        <f t="shared" ref="BB78:BE78" si="229">SUM(BB68:BB77)</f>
+        <f t="shared" ref="BB78:BE78" si="231">SUM(BB68:BB77)</f>
         <v>165987</v>
       </c>
       <c r="BC78" s="6">
-        <f t="shared" si="229"/>
+        <f t="shared" si="231"/>
         <v>164218</v>
       </c>
       <c r="BD78" s="6">
-        <f t="shared" si="229"/>
+        <f t="shared" si="231"/>
         <v>169779</v>
       </c>
       <c r="BE78" s="6">
-        <f t="shared" si="229"/>
+        <f t="shared" si="231"/>
         <v>178894</v>
       </c>
       <c r="BF78" s="6">
@@ -12357,32 +12470,40 @@
         <v>229623</v>
       </c>
       <c r="BK78" s="6">
-        <f t="shared" ref="BK78:BQ78" si="230">SUM(BK68:BK77)</f>
+        <f t="shared" ref="BK78:BS78" si="232">SUM(BK68:BK77)</f>
         <v>222844</v>
       </c>
       <c r="BL78" s="6">
-        <f t="shared" si="230"/>
+        <f t="shared" si="232"/>
         <v>230238</v>
       </c>
       <c r="BM78" s="6">
-        <f t="shared" si="230"/>
+        <f t="shared" si="232"/>
         <v>256408</v>
       </c>
       <c r="BN78" s="6">
-        <f t="shared" si="230"/>
+        <f t="shared" si="232"/>
         <v>276054</v>
       </c>
       <c r="BO78" s="6">
-        <f t="shared" si="230"/>
+        <f t="shared" si="232"/>
         <v>280213</v>
       </c>
       <c r="BP78" s="6">
-        <f t="shared" si="230"/>
+        <f t="shared" si="232"/>
         <v>294744</v>
       </c>
       <c r="BQ78" s="6">
-        <f t="shared" si="230"/>
+        <f t="shared" si="232"/>
         <v>303844</v>
+      </c>
+      <c r="BR78" s="6">
+        <f t="shared" si="232"/>
+        <v>0</v>
+      </c>
+      <c r="BS78" s="6">
+        <f t="shared" si="232"/>
+        <v>395250</v>
       </c>
     </row>
     <row r="79" spans="2:75" x14ac:dyDescent="0.25">
@@ -12393,31 +12514,31 @@
         <v>66</v>
       </c>
       <c r="AY80" s="6">
-        <f t="shared" ref="AY80:BJ80" si="231">AY43</f>
+        <f t="shared" ref="AY80:BJ80" si="233">AY43</f>
         <v>9497</v>
       </c>
       <c r="AZ80" s="6">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>10394</v>
       </c>
       <c r="BA80" s="6">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>9194</v>
       </c>
       <c r="BB80" s="6">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>10285</v>
       </c>
       <c r="BC80" s="6">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>7465</v>
       </c>
       <c r="BD80" s="6">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>6687</v>
       </c>
       <c r="BE80" s="6">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>4395</v>
       </c>
       <c r="BF80" s="6">
@@ -12425,47 +12546,47 @@
         <v>4652</v>
       </c>
       <c r="BG80" s="6">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>8374.1444999999985</v>
       </c>
       <c r="BH80" s="6">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>9658</v>
       </c>
       <c r="BI80" s="6">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>11583</v>
       </c>
       <c r="BJ80" s="6">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>13288.690000000002</v>
       </c>
       <c r="BK80" s="6">
-        <f t="shared" ref="BK80:BQ80" si="232">BK43</f>
+        <f t="shared" ref="BK80:BQ80" si="234">BK43</f>
         <v>12369</v>
       </c>
       <c r="BL80" s="6">
-        <f t="shared" si="232"/>
+        <f t="shared" si="234"/>
         <v>13465</v>
       </c>
       <c r="BM80" s="6">
-        <f t="shared" si="232"/>
+        <f t="shared" si="234"/>
         <v>15688</v>
       </c>
       <c r="BN80" s="6">
-        <f t="shared" si="232"/>
+        <f t="shared" si="234"/>
         <v>20838</v>
       </c>
       <c r="BO80" s="6">
-        <f t="shared" si="232"/>
+        <f t="shared" si="234"/>
         <v>16644</v>
       </c>
       <c r="BP80" s="6">
-        <f t="shared" si="232"/>
+        <f t="shared" si="234"/>
         <v>18337</v>
       </c>
       <c r="BQ80" s="6">
-        <f t="shared" si="232"/>
+        <f t="shared" si="234"/>
         <v>21663</v>
       </c>
     </row>
@@ -12923,79 +13044,79 @@
         <v>68</v>
       </c>
       <c r="AY87" s="6">
-        <f t="shared" ref="AY87:BH87" si="233">SUM(AY81:AY86)</f>
+        <f t="shared" ref="AY87:BH87" si="235">SUM(AY81:AY86)</f>
         <v>12242</v>
       </c>
       <c r="AZ87" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="235"/>
         <v>13247</v>
       </c>
       <c r="BA87" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="235"/>
         <v>14090</v>
       </c>
       <c r="BB87" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="235"/>
         <v>18104</v>
       </c>
       <c r="BC87" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="235"/>
         <v>14076</v>
       </c>
       <c r="BD87" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="235"/>
         <v>12197</v>
       </c>
       <c r="BE87" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="235"/>
         <v>9691</v>
       </c>
       <c r="BF87" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="235"/>
         <v>14511</v>
       </c>
       <c r="BG87" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="235"/>
         <v>13998</v>
       </c>
       <c r="BH87" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="235"/>
         <v>17309</v>
       </c>
       <c r="BI87" s="6">
-        <f t="shared" ref="BI87:BQ87" si="234">SUM(BI81:BI86)</f>
+        <f t="shared" ref="BI87:BQ87" si="236">SUM(BI81:BI86)</f>
         <v>20402</v>
       </c>
       <c r="BJ87" s="6">
-        <f t="shared" si="234"/>
+        <f t="shared" si="236"/>
         <v>19404</v>
       </c>
       <c r="BK87" s="3">
-        <f t="shared" si="234"/>
+        <f t="shared" si="236"/>
         <v>19246</v>
       </c>
       <c r="BL87" s="3">
-        <f t="shared" si="234"/>
+        <f t="shared" si="236"/>
         <v>19370</v>
       </c>
       <c r="BM87" s="3">
-        <f t="shared" si="234"/>
+        <f t="shared" si="236"/>
         <v>24724</v>
       </c>
       <c r="BN87" s="3">
-        <f t="shared" si="234"/>
+        <f t="shared" si="236"/>
         <v>27988</v>
       </c>
       <c r="BO87" s="3">
-        <f t="shared" si="234"/>
+        <f t="shared" si="236"/>
         <v>24026</v>
       </c>
       <c r="BP87" s="3">
-        <f t="shared" si="234"/>
+        <f t="shared" si="236"/>
         <v>25561</v>
       </c>
       <c r="BQ87" s="3">
-        <f t="shared" si="234"/>
+        <f t="shared" si="236"/>
         <v>29999</v>
       </c>
       <c r="CE87" s="3">
@@ -13452,79 +13573,79 @@
       <c r="AW92" s="6"/>
       <c r="AX92" s="6"/>
       <c r="AY92" s="6">
-        <f t="shared" ref="AY92:BJ92" si="235">SUM(AY89:AY91)</f>
+        <f t="shared" ref="AY92:BJ92" si="237">SUM(AY89:AY91)</f>
         <v>-4874</v>
       </c>
       <c r="AZ92" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="237"/>
         <v>-8195</v>
       </c>
       <c r="BA92" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="237"/>
         <v>-330</v>
       </c>
       <c r="BB92" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="237"/>
         <v>5829</v>
       </c>
       <c r="BC92" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="237"/>
         <v>-4779</v>
       </c>
       <c r="BD92" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="237"/>
         <v>-6959</v>
       </c>
       <c r="BE92" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="237"/>
         <v>-9701</v>
       </c>
       <c r="BF92" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="237"/>
         <v>-7531</v>
       </c>
       <c r="BG92" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="237"/>
         <v>-6743</v>
       </c>
       <c r="BH92" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="237"/>
         <v>-5203</v>
       </c>
       <c r="BI92" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="237"/>
         <v>-6077</v>
       </c>
       <c r="BJ92" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="237"/>
         <v>-6472</v>
       </c>
       <c r="BK92" s="3">
-        <f t="shared" ref="BK92:BQ92" si="236">SUM(BK89:BK91)</f>
+        <f t="shared" ref="BK92:BQ92" si="238">SUM(BK89:BK91)</f>
         <v>-8734</v>
       </c>
       <c r="BL92" s="3">
-        <f t="shared" si="236"/>
+        <f t="shared" si="238"/>
         <v>-8298</v>
       </c>
       <c r="BM92" s="3">
-        <f t="shared" si="236"/>
+        <f t="shared" si="238"/>
         <v>-8620</v>
       </c>
       <c r="BN92" s="3">
-        <f t="shared" si="236"/>
+        <f t="shared" si="238"/>
         <v>-21498</v>
       </c>
       <c r="BO92" s="3">
-        <f t="shared" si="236"/>
+        <f t="shared" si="238"/>
         <v>-20010</v>
       </c>
       <c r="BP92" s="3">
-        <f t="shared" si="236"/>
+        <f t="shared" si="238"/>
         <v>-25958</v>
       </c>
       <c r="BQ92" s="3">
-        <f t="shared" si="236"/>
+        <f t="shared" si="238"/>
         <v>-21848</v>
       </c>
     </row>
@@ -14213,79 +14334,79 @@
       <c r="AW99" s="6"/>
       <c r="AX99" s="6"/>
       <c r="AY99" s="6">
-        <f t="shared" ref="AY99:BA99" si="237">SUM(AY94:AY98)</f>
+        <f t="shared" ref="AY99:BA99" si="239">SUM(AY94:AY98)</f>
         <v>-5185</v>
       </c>
       <c r="AZ99" s="6">
-        <f t="shared" si="237"/>
+        <f t="shared" si="239"/>
         <v>-8549</v>
       </c>
       <c r="BA99" s="6">
-        <f t="shared" si="237"/>
+        <f t="shared" si="239"/>
         <v>-15252</v>
       </c>
       <c r="BB99" s="6">
-        <f t="shared" ref="BB99" si="238">SUM(BB94:BB98)</f>
+        <f t="shared" ref="BB99" si="240">SUM(BB94:BB98)</f>
         <v>-21742</v>
       </c>
       <c r="BC99" s="6">
-        <f t="shared" ref="BC99:BQ99" si="239">SUM(BC94:BC98)</f>
+        <f t="shared" ref="BC99:BQ99" si="241">SUM(BC94:BC98)</f>
         <v>-10660</v>
       </c>
       <c r="BD99" s="6">
-        <f t="shared" si="239"/>
+        <f t="shared" si="241"/>
         <v>-6563</v>
       </c>
       <c r="BE99" s="6">
-        <f t="shared" si="239"/>
+        <f t="shared" si="241"/>
         <v>2147</v>
       </c>
       <c r="BF99" s="6">
-        <f t="shared" si="239"/>
+        <f t="shared" si="241"/>
         <v>-7060</v>
       </c>
       <c r="BG99" s="6">
-        <f t="shared" si="239"/>
+        <f t="shared" si="241"/>
         <v>-10516</v>
       </c>
       <c r="BH99" s="6">
-        <f t="shared" si="239"/>
+        <f t="shared" si="241"/>
         <v>5292</v>
       </c>
       <c r="BI99" s="6">
-        <f t="shared" si="239"/>
+        <f t="shared" si="241"/>
         <v>-5875</v>
       </c>
       <c r="BJ99" s="6">
-        <f t="shared" si="239"/>
+        <f t="shared" si="241"/>
         <v>-8401</v>
       </c>
       <c r="BK99" s="3">
-        <f t="shared" si="239"/>
+        <f t="shared" si="241"/>
         <v>-19767</v>
       </c>
       <c r="BL99" s="3">
-        <f t="shared" si="239"/>
+        <f t="shared" si="241"/>
         <v>-11178</v>
       </c>
       <c r="BM99" s="3">
-        <f t="shared" si="239"/>
+        <f t="shared" si="241"/>
         <v>-4371</v>
       </c>
       <c r="BN99" s="3">
-        <f t="shared" si="239"/>
+        <f t="shared" si="241"/>
         <v>-5465</v>
       </c>
       <c r="BO99" s="3">
-        <f t="shared" si="239"/>
+        <f t="shared" si="241"/>
         <v>-19495</v>
       </c>
       <c r="BP99" s="3">
-        <f t="shared" si="239"/>
+        <f t="shared" si="241"/>
         <v>-15977</v>
       </c>
       <c r="BQ99" s="3">
-        <f t="shared" si="239"/>
+        <f t="shared" si="241"/>
         <v>-10047</v>
       </c>
     </row>
@@ -14367,31 +14488,31 @@
         <v>81</v>
       </c>
       <c r="AY101" s="6">
-        <f t="shared" ref="AY101:BJ101" si="240">+AY100+AY99+AY92+AY87</f>
+        <f t="shared" ref="AY101:BJ101" si="242">+AY100+AY99+AY92+AY87</f>
         <v>1937</v>
       </c>
       <c r="AZ101" s="6">
-        <f t="shared" si="240"/>
+        <f t="shared" si="242"/>
         <v>-3380</v>
       </c>
       <c r="BA101" s="6">
-        <f t="shared" si="240"/>
+        <f t="shared" si="242"/>
         <v>-1707</v>
       </c>
       <c r="BB101" s="6">
-        <f t="shared" si="240"/>
+        <f t="shared" si="242"/>
         <v>2061</v>
       </c>
       <c r="BC101" s="6">
-        <f t="shared" si="240"/>
+        <f t="shared" si="242"/>
         <v>-1512</v>
       </c>
       <c r="BD101" s="6">
-        <f t="shared" si="240"/>
+        <f t="shared" si="242"/>
         <v>-1875</v>
       </c>
       <c r="BE101" s="6">
-        <f t="shared" si="240"/>
+        <f t="shared" si="242"/>
         <v>1773</v>
       </c>
       <c r="BF101" s="6">
@@ -14399,47 +14520,47 @@
         <v>345</v>
       </c>
       <c r="BG101" s="6">
-        <f t="shared" si="240"/>
+        <f t="shared" si="242"/>
         <v>-3176</v>
       </c>
       <c r="BH101" s="6">
-        <f t="shared" si="240"/>
+        <f t="shared" si="242"/>
         <v>17384</v>
       </c>
       <c r="BI101" s="6">
-        <f t="shared" si="240"/>
+        <f t="shared" si="242"/>
         <v>8096</v>
       </c>
       <c r="BJ101" s="6">
-        <f t="shared" si="240"/>
+        <f t="shared" si="242"/>
         <v>4927</v>
       </c>
       <c r="BK101" s="3">
-        <f t="shared" ref="BK101:BQ101" si="241">+BK100+BK99+BK92+BK87</f>
+        <f t="shared" ref="BK101:BQ101" si="243">+BK100+BK99+BK92+BK87</f>
         <v>-9543</v>
       </c>
       <c r="BL101" s="3">
-        <f t="shared" si="241"/>
+        <f t="shared" si="243"/>
         <v>-258</v>
       </c>
       <c r="BM101" s="3">
-        <f t="shared" si="241"/>
+        <f t="shared" si="243"/>
         <v>12101</v>
       </c>
       <c r="BN101" s="3">
-        <f t="shared" si="241"/>
+        <f t="shared" si="243"/>
         <v>311</v>
       </c>
       <c r="BO101" s="3">
-        <f t="shared" si="241"/>
+        <f t="shared" si="243"/>
         <v>-15367</v>
       </c>
       <c r="BP101" s="3">
-        <f t="shared" si="241"/>
+        <f t="shared" si="243"/>
         <v>-16243</v>
       </c>
       <c r="BQ101" s="3">
-        <f t="shared" si="241"/>
+        <f t="shared" si="243"/>
         <v>-1887</v>
       </c>
     </row>
@@ -14556,55 +14677,55 @@
         <v>199</v>
       </c>
       <c r="BC104" s="6">
-        <f t="shared" ref="BC104:BO104" si="242">+BC103-BB103</f>
+        <f t="shared" ref="BC104:BO104" si="244">+BC103-BB103</f>
         <v>5835</v>
       </c>
       <c r="BD104" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="244"/>
         <v>5748</v>
       </c>
       <c r="BE104" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="244"/>
         <v>3761</v>
       </c>
       <c r="BF104" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="244"/>
         <v>-1314</v>
       </c>
       <c r="BG104" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="244"/>
         <v>-8886</v>
       </c>
       <c r="BH104" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="244"/>
         <v>-5645</v>
       </c>
       <c r="BI104" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="244"/>
         <v>-5284</v>
       </c>
       <c r="BJ104" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="244"/>
         <v>1132</v>
       </c>
       <c r="BK104" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="244"/>
         <v>2012</v>
       </c>
       <c r="BL104" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="244"/>
         <v>1470</v>
       </c>
       <c r="BM104" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="244"/>
         <v>1605</v>
       </c>
       <c r="BN104" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="244"/>
         <v>1663</v>
       </c>
       <c r="BO104" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="244"/>
         <v>2767</v>
       </c>
     </row>
@@ -14621,51 +14742,51 @@
         <v>7970</v>
       </c>
       <c r="AZ106" s="6">
-        <f t="shared" ref="AZ106:BC106" si="243">+AZ87+AZ89</f>
+        <f t="shared" ref="AZ106:BC106" si="245">+AZ87+AZ89</f>
         <v>8635</v>
       </c>
       <c r="BA106" s="6">
-        <f t="shared" si="243"/>
+        <f t="shared" si="245"/>
         <v>9776</v>
       </c>
       <c r="BB106" s="6">
-        <f t="shared" si="243"/>
+        <f t="shared" si="245"/>
         <v>12734</v>
       </c>
       <c r="BC106" s="6">
-        <f t="shared" si="243"/>
+        <f t="shared" si="245"/>
         <v>8761</v>
       </c>
       <c r="BD106" s="6">
-        <f t="shared" ref="BD106:BJ106" si="244">+BD87+BD89</f>
+        <f t="shared" ref="BD106:BJ106" si="246">+BD87+BD89</f>
         <v>4669</v>
       </c>
       <c r="BE106" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="246"/>
         <v>336</v>
       </c>
       <c r="BF106" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="246"/>
         <v>5523</v>
       </c>
       <c r="BG106" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="246"/>
         <v>7175</v>
       </c>
       <c r="BH106" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="246"/>
         <v>11175</v>
       </c>
       <c r="BI106" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="246"/>
         <v>13906</v>
       </c>
       <c r="BJ106" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="246"/>
         <v>11812</v>
       </c>
       <c r="BK106" s="3">
-        <f t="shared" ref="BK106" si="245">+BK87+BK89</f>
+        <f t="shared" ref="BK106" si="247">+BK87+BK89</f>
         <v>12846</v>
       </c>
       <c r="BL106" s="3">
@@ -14685,11 +14806,11 @@
         <v>11085</v>
       </c>
       <c r="BP106" s="3">
-        <f t="shared" ref="BP106:BQ106" si="246">+BP87+BP89</f>
+        <f t="shared" ref="BP106:BQ106" si="248">+BP87+BP89</f>
         <v>9023</v>
       </c>
       <c r="BQ106" s="3">
-        <f t="shared" si="246"/>
+        <f t="shared" si="248"/>
         <v>11170</v>
       </c>
     </row>
@@ -14698,11 +14819,11 @@
         <v>127</v>
       </c>
       <c r="BB107" s="6">
-        <f t="shared" ref="BB107:BC107" si="247">SUM(AY106:BB106)</f>
+        <f t="shared" ref="BB107:BC107" si="249">SUM(AY106:BB106)</f>
         <v>39115</v>
       </c>
       <c r="BC107" s="6">
-        <f t="shared" si="247"/>
+        <f t="shared" si="249"/>
         <v>39906</v>
       </c>
       <c r="BD107" s="6">
@@ -14718,31 +14839,31 @@
         <v>19289</v>
       </c>
       <c r="BG107" s="6">
-        <f t="shared" ref="BG107:BK107" si="248">SUM(BD106:BG106)</f>
+        <f t="shared" ref="BG107:BK107" si="250">SUM(BD106:BG106)</f>
         <v>17703</v>
       </c>
       <c r="BH107" s="6">
-        <f t="shared" si="248"/>
+        <f t="shared" si="250"/>
         <v>24209</v>
       </c>
       <c r="BI107" s="6">
-        <f t="shared" si="248"/>
+        <f t="shared" si="250"/>
         <v>37779</v>
       </c>
       <c r="BJ107" s="6">
-        <f t="shared" si="248"/>
+        <f t="shared" si="250"/>
         <v>44068</v>
       </c>
       <c r="BK107" s="6">
-        <f t="shared" si="248"/>
+        <f t="shared" si="250"/>
         <v>49739</v>
       </c>
       <c r="BL107" s="3">
-        <f t="shared" ref="BL107:BM107" si="249">SUM(BI106:BL106)</f>
+        <f t="shared" ref="BL107:BM107" si="251">SUM(BI106:BL106)</f>
         <v>49761</v>
       </c>
       <c r="BM107" s="3">
-        <f t="shared" si="249"/>
+        <f t="shared" si="251"/>
         <v>52321</v>
       </c>
       <c r="BN107" s="3">
@@ -14754,11 +14875,11 @@
         <v>52311</v>
       </c>
       <c r="BP107" s="3">
-        <f t="shared" ref="BP107:BQ107" si="250">SUM(BM106:BP106)</f>
+        <f t="shared" ref="BP107:BQ107" si="252">SUM(BM106:BP106)</f>
         <v>50137</v>
       </c>
       <c r="BQ107" s="3">
-        <f t="shared" si="250"/>
+        <f t="shared" si="252"/>
         <v>44841</v>
       </c>
     </row>
@@ -14784,11 +14905,11 @@
         <v>0.3108555104495565</v>
       </c>
       <c r="BP108" s="19">
-        <f t="shared" ref="BP108:BQ108" si="251">+BP107/BD107-1</f>
+        <f t="shared" ref="BP108:BQ108" si="253">+BP107/BD107-1</f>
         <v>0.39501947690595429</v>
       </c>
       <c r="BQ108" s="19">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>0.69211320754716987</v>
       </c>
     </row>
@@ -14817,59 +14938,59 @@
         <v>94400</v>
       </c>
       <c r="AZ110" s="3">
-        <f t="shared" ref="AZ110:BM110" si="252">SUM(AW32:AZ32)</f>
+        <f t="shared" ref="AZ110:BM110" si="254">SUM(AW32:AZ32)</f>
         <v>104790</v>
       </c>
       <c r="BA110" s="3">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>112330</v>
       </c>
       <c r="BB110" s="3">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>117929</v>
       </c>
       <c r="BC110" s="3">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>119666</v>
       </c>
       <c r="BD110" s="3">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>119411</v>
       </c>
       <c r="BE110" s="3">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>118115</v>
       </c>
       <c r="BF110" s="3">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>116609</v>
       </c>
       <c r="BG110" s="3">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>117346</v>
       </c>
       <c r="BH110" s="3">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>120523</v>
       </c>
       <c r="BI110" s="3">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>126955</v>
       </c>
       <c r="BJ110" s="3">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>134901</v>
       </c>
       <c r="BK110" s="3">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>142711</v>
       </c>
       <c r="BL110" s="3">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>149783</v>
       </c>
       <c r="BM110" s="3">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>156226</v>
       </c>
       <c r="BN110" s="3">
@@ -14890,7 +15011,7 @@
       </c>
       <c r="BR110" s="3">
         <f>SUM(BO32:BR32)</f>
-        <v>195263.2</v>
+        <v>200965</v>
       </c>
       <c r="BS110" s="3"/>
       <c r="BT110" s="3"/>
